--- a/data/New Import Monitoring.xlsx
+++ b/data/New Import Monitoring.xlsx
@@ -5,17 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\overs\Dropbox\Marfani Projects\Marfani Steel Reportings\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User-2\Dropbox\Marfani Projects\Marfani Steel Reportings\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EE4ECC-1457-4388-A4EB-3F7A122336B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6732E89-80D0-4B5B-A2E6-2E5B639AFE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A600BC22-BC84-4799-95E7-AAC4792B97D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Compele Data Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Compele Data Sheet'!$A$3:$CV$127</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5601" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5606" uniqueCount="1175">
   <si>
     <t>Marfani Steel Private Limited</t>
   </si>
@@ -1830,9 +1833,6 @@
     <t>TALGMJ03090785</t>
   </si>
   <si>
-    <t>Surrenderred</t>
-  </si>
-  <si>
     <t>WASTE &amp; SCRAP (CU NI CLADDING 11%-14%)</t>
   </si>
   <si>
@@ -3633,9 +3633,6 @@
     <t>GFS ROJA  0011</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>Nickel Alloys Scrap for Melting Purpose (REFORMER TUBE)</t>
   </si>
   <si>
@@ -3703,6 +3700,12 @@
   </si>
   <si>
     <t>Citylink</t>
+  </si>
+  <si>
+    <t>Cha Invoice Pending, DEBIT ADVOICE AMT</t>
+  </si>
+  <si>
+    <t>MOSSIMS210926691496</t>
   </si>
 </sst>
 </file>
@@ -5391,7 +5394,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="5" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A5" s="12" t="s">
         <v>95</v>
       </c>
@@ -5709,7 +5712,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="6" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A6" s="12" t="s">
         <v>95</v>
       </c>
@@ -6024,7 +6027,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="7" spans="1:100" s="13" customFormat="1" ht="72">
       <c r="A7" s="12" t="s">
         <v>95</v>
       </c>
@@ -6665,7 +6668,7 @@
       </c>
       <c r="CV8" s="29"/>
     </row>
-    <row r="9" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="9" spans="1:100" s="13" customFormat="1" ht="72">
       <c r="A9" s="12" t="s">
         <v>95</v>
       </c>
@@ -6984,7 +6987,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="10" spans="1:100" s="13" customFormat="1" ht="100.8">
       <c r="A10" s="12" t="s">
         <v>95</v>
       </c>
@@ -7303,7 +7306,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:100" s="13" customFormat="1" ht="345.6">
+    <row r="11" spans="1:100" s="13" customFormat="1" ht="57.6">
       <c r="A11" s="12" t="s">
         <v>95</v>
       </c>
@@ -7612,7 +7615,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="12" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A12" s="12" t="s">
         <v>95</v>
       </c>
@@ -7929,7 +7932,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="13" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A13" s="12" t="s">
         <v>95</v>
       </c>
@@ -8245,7 +8248,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="14" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="14" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A14" s="12" t="s">
         <v>95</v>
       </c>
@@ -8563,7 +8566,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="15" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A15" s="12" t="s">
         <v>95</v>
       </c>
@@ -8881,7 +8884,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="16" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="16" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A16" s="12" t="s">
         <v>95</v>
       </c>
@@ -9203,7 +9206,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="17" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A17" s="12" t="s">
         <v>95</v>
       </c>
@@ -9522,7 +9525,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="18" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="18" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A18" s="12" t="s">
         <v>95</v>
       </c>
@@ -9840,7 +9843,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="19" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A19" s="12" t="s">
         <v>95</v>
       </c>
@@ -10159,7 +10162,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="20" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A20" s="12" t="s">
         <v>288</v>
       </c>
@@ -10477,7 +10480,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="21" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="21" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A21" s="12" t="s">
         <v>288</v>
       </c>
@@ -17499,7 +17502,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="43" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="43" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A43" s="12" t="s">
         <v>288</v>
       </c>
@@ -17817,7 +17820,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="44" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="44" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A44" s="12" t="s">
         <v>288</v>
       </c>
@@ -18135,7 +18138,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="45" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="45" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A45" s="12" t="s">
         <v>288</v>
       </c>
@@ -18453,7 +18456,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="46" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="46" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A46" s="12" t="s">
         <v>288</v>
       </c>
@@ -18478,7 +18481,7 @@
         <v>46305</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>172</v>
@@ -18503,10 +18506,10 @@
         <v>102</v>
       </c>
       <c r="Q46" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="R46" s="42" t="s">
         <v>574</v>
-      </c>
-      <c r="R46" s="42" t="s">
-        <v>575</v>
       </c>
       <c r="S46" s="13" t="s">
         <v>274</v>
@@ -18529,19 +18532,19 @@
         <v>429000</v>
       </c>
       <c r="Y46" s="19" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="Z46" s="14">
         <v>46179</v>
       </c>
       <c r="AA46" s="13" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AB46" s="13">
         <v>25.41</v>
       </c>
       <c r="AC46" s="13" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AD46" s="13">
         <v>25.01</v>
@@ -18568,13 +18571,13 @@
         <v>50420</v>
       </c>
       <c r="AL46" s="16" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AM46" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN46" s="47" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AP46" s="13" t="s">
         <v>115</v>
@@ -18598,7 +18601,7 @@
         <v>800</v>
       </c>
       <c r="AX46" s="16" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="BA46" s="13">
         <v>50.42</v>
@@ -18654,7 +18657,7 @@
       </c>
       <c r="BQ46" s="24"/>
       <c r="BR46" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS46" s="13" t="s">
         <v>169</v>
@@ -18727,7 +18730,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="47" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A47" s="12" t="s">
         <v>288</v>
       </c>
@@ -18742,7 +18745,7 @@
         <v>97</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F47" s="43">
         <v>46254</v>
@@ -18780,10 +18783,10 @@
         <v>102</v>
       </c>
       <c r="Q47" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="R47" s="42" t="s">
         <v>574</v>
-      </c>
-      <c r="R47" s="42" t="s">
-        <v>575</v>
       </c>
       <c r="S47" s="13" t="s">
         <v>274</v>
@@ -18806,19 +18809,19 @@
         <v>429000</v>
       </c>
       <c r="Y47" s="19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="Z47" s="14">
         <v>46179</v>
       </c>
       <c r="AA47" s="13" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AB47" s="13">
         <v>24.95</v>
       </c>
       <c r="AC47" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AD47" s="13">
         <v>25.17</v>
@@ -18845,16 +18848,16 @@
         <v>50120</v>
       </c>
       <c r="AL47" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AM47" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN47" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="AO47" s="13" t="s">
         <v>588</v>
-      </c>
-      <c r="AO47" s="13" t="s">
-        <v>589</v>
       </c>
       <c r="AP47" s="13" t="s">
         <v>115</v>
@@ -18872,7 +18875,7 @@
         <v>117</v>
       </c>
       <c r="AU47" s="13" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AV47" s="13" t="s">
         <v>119</v>
@@ -18881,10 +18884,10 @@
         <v>800</v>
       </c>
       <c r="AX47" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="AY47" s="16" t="s">
         <v>591</v>
-      </c>
-      <c r="AY47" s="16" t="s">
-        <v>592</v>
       </c>
       <c r="AZ47" s="14">
         <v>46247</v>
@@ -18967,7 +18970,7 @@
         <v>127</v>
       </c>
       <c r="BX47" s="13" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="BY47" s="13" t="s">
         <v>124</v>
@@ -19039,13 +19042,13 @@
         <v>110</v>
       </c>
       <c r="CU47" s="13" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="CV47" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="48" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A48" s="12" t="s">
         <v>288</v>
       </c>
@@ -19060,7 +19063,7 @@
         <v>97</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F48" s="43">
         <v>46220</v>
@@ -19098,10 +19101,10 @@
         <v>102</v>
       </c>
       <c r="Q48" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="R48" s="42" t="s">
         <v>574</v>
-      </c>
-      <c r="R48" s="42" t="s">
-        <v>575</v>
       </c>
       <c r="S48" s="13" t="s">
         <v>274</v>
@@ -19124,19 +19127,19 @@
         <v>429000</v>
       </c>
       <c r="Y48" s="19" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="Z48" s="14">
         <v>46179</v>
       </c>
       <c r="AA48" s="13" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AB48" s="13">
         <v>24.95</v>
       </c>
       <c r="AC48" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AD48" s="13">
         <v>24.41</v>
@@ -19163,16 +19166,16 @@
         <v>49360</v>
       </c>
       <c r="AL48" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AM48" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN48" s="47" t="s">
+        <v>598</v>
+      </c>
+      <c r="AO48" s="16" t="s">
         <v>599</v>
-      </c>
-      <c r="AO48" s="16" t="s">
-        <v>600</v>
       </c>
       <c r="AP48" s="13" t="s">
         <v>115</v>
@@ -19190,7 +19193,7 @@
         <v>117</v>
       </c>
       <c r="AU48" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AV48" s="13" t="s">
         <v>119</v>
@@ -19199,10 +19202,10 @@
         <v>800</v>
       </c>
       <c r="AX48" s="13" t="s">
+        <v>601</v>
+      </c>
+      <c r="AY48" s="16" t="s">
         <v>602</v>
-      </c>
-      <c r="AY48" s="16" t="s">
-        <v>603</v>
       </c>
       <c r="AZ48" s="14">
         <v>46214</v>
@@ -19361,10 +19364,10 @@
         <v>110</v>
       </c>
       <c r="CU48" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
-    <row r="49" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="49" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A49" s="12" t="s">
         <v>288</v>
       </c>
@@ -19379,7 +19382,7 @@
         <v>97</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F49" s="43">
         <v>46254</v>
@@ -19417,10 +19420,10 @@
         <v>102</v>
       </c>
       <c r="Q49" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="R49" s="42" t="s">
         <v>574</v>
-      </c>
-      <c r="R49" s="42" t="s">
-        <v>575</v>
       </c>
       <c r="S49" s="13" t="s">
         <v>274</v>
@@ -19443,19 +19446,19 @@
         <v>429000</v>
       </c>
       <c r="Y49" s="19" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="Z49" s="14">
         <v>46180</v>
       </c>
       <c r="AA49" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AB49" s="13">
         <v>24.82</v>
       </c>
       <c r="AC49" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AD49" s="13">
         <v>25.38</v>
@@ -19482,16 +19485,16 @@
         <v>50200</v>
       </c>
       <c r="AL49" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AM49" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN49" s="47" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AO49" s="13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AP49" s="13" t="s">
         <v>115</v>
@@ -19509,7 +19512,7 @@
         <v>117</v>
       </c>
       <c r="AU49" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AV49" s="13" t="s">
         <v>119</v>
@@ -19518,10 +19521,10 @@
         <v>800</v>
       </c>
       <c r="AX49" s="13" t="s">
+        <v>610</v>
+      </c>
+      <c r="AY49" s="16" t="s">
         <v>611</v>
-      </c>
-      <c r="AY49" s="16" t="s">
-        <v>612</v>
       </c>
       <c r="AZ49" s="14">
         <v>46247</v>
@@ -19604,7 +19607,7 @@
         <v>127</v>
       </c>
       <c r="BX49" s="13" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="BY49" s="13" t="s">
         <v>124</v>
@@ -19676,13 +19679,13 @@
         <v>110</v>
       </c>
       <c r="CU49" s="13" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="CV49" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="50" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="50" spans="1:100" s="13" customFormat="1" ht="72">
       <c r="A50" s="12" t="s">
         <v>288</v>
       </c>
@@ -19697,7 +19700,7 @@
         <v>97</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F50" s="43">
         <v>46220</v>
@@ -19735,10 +19738,10 @@
         <v>102</v>
       </c>
       <c r="Q50" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="R50" s="42" t="s">
         <v>574</v>
-      </c>
-      <c r="R50" s="42" t="s">
-        <v>575</v>
       </c>
       <c r="S50" s="13" t="s">
         <v>274</v>
@@ -19761,25 +19764,25 @@
         <v>429000</v>
       </c>
       <c r="Y50" s="19" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="Z50" s="14">
         <v>46180</v>
       </c>
       <c r="AA50" s="13" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AB50" s="13">
         <v>24.89</v>
       </c>
       <c r="AC50" s="13" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AD50" s="13">
         <v>24.95</v>
       </c>
       <c r="AE50" s="13" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AF50" s="13">
         <v>25.24</v>
@@ -19800,16 +19803,16 @@
         <v>75080</v>
       </c>
       <c r="AL50" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AM50" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN50" s="16" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AO50" s="16" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AP50" s="13" t="s">
         <v>115</v>
@@ -19827,7 +19830,7 @@
         <v>117</v>
       </c>
       <c r="AU50" s="13" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AV50" s="13" t="s">
         <v>119</v>
@@ -19836,10 +19839,10 @@
         <v>800</v>
       </c>
       <c r="AX50" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="AY50" s="16" t="s">
         <v>622</v>
-      </c>
-      <c r="AY50" s="16" t="s">
-        <v>623</v>
       </c>
       <c r="AZ50" s="14">
         <v>46214</v>
@@ -19997,10 +20000,10 @@
         <v>110</v>
       </c>
       <c r="CU50" s="13" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
-    <row r="51" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="51" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A51" s="12" t="s">
         <v>288</v>
       </c>
@@ -20015,7 +20018,7 @@
         <v>97</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F51" s="43">
         <v>46223</v>
@@ -20053,10 +20056,10 @@
         <v>102</v>
       </c>
       <c r="Q51" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="R51" s="42" t="s">
         <v>574</v>
-      </c>
-      <c r="R51" s="42" t="s">
-        <v>575</v>
       </c>
       <c r="S51" s="13" t="s">
         <v>274</v>
@@ -20085,7 +20088,7 @@
         <v>46183</v>
       </c>
       <c r="AA51" s="13" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AB51" s="13">
         <v>25.01</v>
@@ -20118,16 +20121,16 @@
         <v>25010</v>
       </c>
       <c r="AL51" s="13" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AM51" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN51" s="47" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AO51" s="16" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AP51" s="13" t="s">
         <v>115</v>
@@ -20145,7 +20148,7 @@
         <v>117</v>
       </c>
       <c r="AU51" s="13" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AV51" s="13" t="s">
         <v>119</v>
@@ -20154,7 +20157,7 @@
         <v>800</v>
       </c>
       <c r="AX51" s="13" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AY51" s="13">
         <v>9000102175</v>
@@ -20315,10 +20318,10 @@
         <v>110</v>
       </c>
       <c r="CU51" s="13" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
-    <row r="52" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="52" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A52" s="12" t="s">
         <v>288</v>
       </c>
@@ -20333,7 +20336,7 @@
         <v>97</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F52" s="43">
         <v>46266</v>
@@ -20371,13 +20374,13 @@
         <v>102</v>
       </c>
       <c r="Q52" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="R52" s="42" t="s">
         <v>633</v>
       </c>
-      <c r="R52" s="42" t="s">
+      <c r="S52" s="13" t="s">
         <v>634</v>
-      </c>
-      <c r="S52" s="13" t="s">
-        <v>635</v>
       </c>
       <c r="T52" s="24">
         <v>200</v>
@@ -20397,19 +20400,19 @@
         <v>146000</v>
       </c>
       <c r="Y52" s="19" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="Z52" s="14">
         <v>46179</v>
       </c>
       <c r="AA52" s="13" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AB52" s="13">
         <v>25.06</v>
       </c>
       <c r="AC52" s="13" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AD52" s="13">
         <v>25.35</v>
@@ -20436,16 +20439,16 @@
         <v>50410</v>
       </c>
       <c r="AL52" s="16" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AM52" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN52" s="16" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AO52" s="13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AP52" s="13" t="s">
         <v>115</v>
@@ -20463,7 +20466,7 @@
         <v>117</v>
       </c>
       <c r="AU52" s="13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AV52" s="13" t="s">
         <v>119</v>
@@ -20472,10 +20475,10 @@
         <v>800</v>
       </c>
       <c r="AX52" s="13" t="s">
+        <v>641</v>
+      </c>
+      <c r="AY52" s="16" t="s">
         <v>642</v>
-      </c>
-      <c r="AY52" s="16" t="s">
-        <v>643</v>
       </c>
       <c r="AZ52" s="14">
         <v>46247</v>
@@ -20558,7 +20561,7 @@
         <v>127</v>
       </c>
       <c r="BX52" s="13" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="BY52" s="13" t="s">
         <v>124</v>
@@ -20630,13 +20633,13 @@
         <v>110</v>
       </c>
       <c r="CU52" s="13" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="CV52" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="53" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="53" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A53" s="12" t="s">
         <v>288</v>
       </c>
@@ -20651,7 +20654,7 @@
         <v>97</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F53" s="43">
         <v>46268</v>
@@ -20689,13 +20692,13 @@
         <v>102</v>
       </c>
       <c r="Q53" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="R53" s="42" t="s">
         <v>633</v>
       </c>
-      <c r="R53" s="42" t="s">
+      <c r="S53" s="13" t="s">
         <v>634</v>
-      </c>
-      <c r="S53" s="13" t="s">
-        <v>635</v>
       </c>
       <c r="T53" s="24">
         <v>200</v>
@@ -20721,13 +20724,13 @@
         <v>46247</v>
       </c>
       <c r="AA53" s="13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AB53" s="13">
         <v>24.51</v>
       </c>
       <c r="AC53" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AD53" s="13">
         <v>25.15</v>
@@ -20754,16 +20757,16 @@
         <v>49660</v>
       </c>
       <c r="AL53" s="16" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AM53" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN53" s="16" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AO53" s="13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AP53" s="13" t="s">
         <v>115</v>
@@ -20781,7 +20784,7 @@
         <v>117</v>
       </c>
       <c r="AU53" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AV53" s="13" t="s">
         <v>119</v>
@@ -20790,10 +20793,10 @@
         <v>800</v>
       </c>
       <c r="AX53" s="13" t="s">
+        <v>650</v>
+      </c>
+      <c r="AY53" s="16" t="s">
         <v>651</v>
-      </c>
-      <c r="AY53" s="16" t="s">
-        <v>652</v>
       </c>
       <c r="AZ53" s="14">
         <v>46247</v>
@@ -20876,7 +20879,7 @@
         <v>127</v>
       </c>
       <c r="BX53" s="13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="BY53" s="13" t="s">
         <v>124</v>
@@ -20948,13 +20951,13 @@
         <v>110</v>
       </c>
       <c r="CU53" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="CV53" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="54" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="54" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A54" s="12" t="s">
         <v>288</v>
       </c>
@@ -20969,7 +20972,7 @@
         <v>97</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F54" s="43">
         <v>46267</v>
@@ -21007,13 +21010,13 @@
         <v>102</v>
       </c>
       <c r="Q54" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="R54" s="42" t="s">
         <v>633</v>
       </c>
-      <c r="R54" s="42" t="s">
+      <c r="S54" s="13" t="s">
         <v>634</v>
-      </c>
-      <c r="S54" s="13" t="s">
-        <v>635</v>
       </c>
       <c r="T54" s="24">
         <v>200</v>
@@ -21033,19 +21036,19 @@
         <v>146000</v>
       </c>
       <c r="Y54" s="19" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Z54" s="14">
         <v>46180</v>
       </c>
       <c r="AA54" s="13" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AB54" s="13">
         <v>24.8</v>
       </c>
       <c r="AC54" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AD54" s="13">
         <v>25.07</v>
@@ -21072,16 +21075,16 @@
         <v>49870</v>
       </c>
       <c r="AL54" s="16" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AM54" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN54" s="16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AO54" s="13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AP54" s="13" t="s">
         <v>115</v>
@@ -21099,7 +21102,7 @@
         <v>117</v>
       </c>
       <c r="AU54" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AV54" s="13" t="s">
         <v>119</v>
@@ -21108,10 +21111,10 @@
         <v>800</v>
       </c>
       <c r="AX54" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="AY54" s="16" t="s">
         <v>661</v>
-      </c>
-      <c r="AY54" s="16" t="s">
-        <v>662</v>
       </c>
       <c r="AZ54" s="14">
         <v>46247</v>
@@ -21194,7 +21197,7 @@
         <v>127</v>
       </c>
       <c r="BX54" s="13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="BY54" s="13" t="s">
         <v>124</v>
@@ -21266,13 +21269,13 @@
         <v>110</v>
       </c>
       <c r="CU54" s="13" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="CV54" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="55" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="55" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A55" s="12" t="s">
         <v>288</v>
       </c>
@@ -21287,7 +21290,7 @@
         <v>97</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F55" s="43">
         <v>46292</v>
@@ -21297,7 +21300,7 @@
         <v>46305</v>
       </c>
       <c r="H55" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>172</v>
@@ -21322,13 +21325,13 @@
         <v>102</v>
       </c>
       <c r="Q55" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="R55" s="42" t="s">
         <v>633</v>
       </c>
-      <c r="R55" s="42" t="s">
+      <c r="S55" s="13" t="s">
         <v>634</v>
-      </c>
-      <c r="S55" s="13" t="s">
-        <v>635</v>
       </c>
       <c r="T55" s="24">
         <v>200</v>
@@ -21354,13 +21357,13 @@
         <v>110</v>
       </c>
       <c r="AA55" s="13" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AB55" s="45">
         <v>25.24</v>
       </c>
       <c r="AC55" s="13" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AD55" s="45">
         <v>25.2</v>
@@ -21387,7 +21390,7 @@
         <v>50440</v>
       </c>
       <c r="AL55" s="16" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AM55" s="13" t="s">
         <v>112</v>
@@ -21417,7 +21420,7 @@
         <v>800</v>
       </c>
       <c r="AX55" s="13" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="BA55" s="45">
         <v>50.44</v>
@@ -21471,7 +21474,7 @@
       </c>
       <c r="BQ55" s="24"/>
       <c r="BR55" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS55" s="13" t="s">
         <v>169</v>
@@ -21483,13 +21486,13 @@
         <v>299</v>
       </c>
       <c r="BV55" s="13" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="BW55" s="16" t="s">
         <v>127</v>
       </c>
       <c r="BX55" s="13" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="BY55" s="13" t="s">
         <v>124</v>
@@ -21547,7 +21550,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="56" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A56" s="12" t="s">
         <v>288</v>
       </c>
@@ -21632,7 +21635,7 @@
         <v>46190</v>
       </c>
       <c r="AA56" s="13" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AB56" s="13">
         <v>24.986000000000001</v>
@@ -21659,7 +21662,7 @@
         <v>24986</v>
       </c>
       <c r="AL56" s="13" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AM56" s="13" t="s">
         <v>246</v>
@@ -21668,7 +21671,7 @@
         <v>20463</v>
       </c>
       <c r="AO56" s="16" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AP56" s="13" t="s">
         <v>115</v>
@@ -21686,7 +21689,7 @@
         <v>117</v>
       </c>
       <c r="AU56" s="13" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AV56" s="13" t="s">
         <v>119</v>
@@ -21695,7 +21698,7 @@
         <v>800</v>
       </c>
       <c r="AX56" s="13" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AY56" s="13">
         <v>9000102140</v>
@@ -21855,13 +21858,13 @@
         <v>110</v>
       </c>
       <c r="CU56" s="13" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="CV56" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="57" spans="1:100" s="13" customFormat="1" ht="100.8">
       <c r="A57" s="12" t="s">
         <v>288</v>
       </c>
@@ -21876,7 +21879,7 @@
         <v>97</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F57" s="43">
         <v>46223</v>
@@ -21940,31 +21943,31 @@
         <v>286000</v>
       </c>
       <c r="Y57" s="19" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Z57" s="14">
         <v>46183</v>
       </c>
       <c r="AA57" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AB57" s="13">
         <v>24.97</v>
       </c>
       <c r="AC57" s="13" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AD57" s="13">
         <v>24.72</v>
       </c>
       <c r="AE57" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AF57" s="13">
         <v>24.64</v>
       </c>
       <c r="AG57" s="13" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AH57" s="13">
         <v>24.94</v>
@@ -21979,16 +21982,16 @@
         <v>99270</v>
       </c>
       <c r="AL57" s="16" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AM57" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN57" s="16" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AO57" s="16" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AP57" s="13" t="s">
         <v>115</v>
@@ -22006,7 +22009,7 @@
         <v>117</v>
       </c>
       <c r="AU57" s="13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AV57" s="13" t="s">
         <v>119</v>
@@ -22015,10 +22018,10 @@
         <v>800</v>
       </c>
       <c r="AX57" s="13" t="s">
+        <v>684</v>
+      </c>
+      <c r="AY57" s="16" t="s">
         <v>685</v>
-      </c>
-      <c r="AY57" s="16" t="s">
-        <v>686</v>
       </c>
       <c r="AZ57" s="14">
         <v>46214</v>
@@ -22101,7 +22104,7 @@
         <v>127</v>
       </c>
       <c r="BX57" s="13" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="BY57" s="13" t="s">
         <v>124</v>
@@ -22176,10 +22179,10 @@
         <v>110</v>
       </c>
       <c r="CU57" s="13" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
-    <row r="58" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="58" spans="1:100" s="13" customFormat="1" ht="100.8">
       <c r="A58" s="12" t="s">
         <v>288</v>
       </c>
@@ -22194,7 +22197,7 @@
         <v>97</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F58" s="43">
         <v>46260</v>
@@ -22258,31 +22261,31 @@
         <v>286000</v>
       </c>
       <c r="Y58" s="19" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="Z58" s="14">
         <v>46184</v>
       </c>
       <c r="AA58" s="13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AB58" s="13">
         <v>24.98</v>
       </c>
       <c r="AC58" s="13" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AD58" s="13">
         <v>24.98</v>
       </c>
       <c r="AE58" s="13" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AF58" s="13">
         <v>24.88</v>
       </c>
       <c r="AG58" s="13" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AH58" s="13">
         <v>24.97</v>
@@ -22297,16 +22300,16 @@
         <v>99810</v>
       </c>
       <c r="AL58" s="16" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AM58" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN58" s="16" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AO58" s="16" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AP58" s="13" t="s">
         <v>115</v>
@@ -22324,7 +22327,7 @@
         <v>117</v>
       </c>
       <c r="AU58" s="13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AV58" s="13" t="s">
         <v>119</v>
@@ -22333,10 +22336,10 @@
         <v>800</v>
       </c>
       <c r="AX58" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="AY58" s="16" t="s">
         <v>697</v>
-      </c>
-      <c r="AY58" s="16" t="s">
-        <v>698</v>
       </c>
       <c r="AZ58" s="14">
         <v>46214</v>
@@ -22419,7 +22422,7 @@
         <v>127</v>
       </c>
       <c r="BX58" s="13" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="BY58" s="13" t="s">
         <v>124</v>
@@ -22494,10 +22497,10 @@
         <v>110</v>
       </c>
       <c r="CU58" s="13" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
-    <row r="59" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="59" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A59" s="12" t="s">
         <v>288</v>
       </c>
@@ -22512,7 +22515,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F59" s="14">
         <v>46266</v>
@@ -22553,7 +22556,7 @@
         <v>445</v>
       </c>
       <c r="R59" s="13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="S59" s="13" t="s">
         <v>105</v>
@@ -22576,19 +22579,19 @@
         <v>38250</v>
       </c>
       <c r="Y59" s="19" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="Z59" s="14">
         <v>46174</v>
       </c>
       <c r="AA59" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AB59" s="13">
         <v>25.57</v>
       </c>
       <c r="AC59" s="13" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AD59" s="13">
         <v>24.27</v>
@@ -22615,16 +22618,16 @@
         <v>49840</v>
       </c>
       <c r="AL59" s="13" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AM59" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN59" s="16" t="s">
+        <v>706</v>
+      </c>
+      <c r="AO59" s="13" t="s">
         <v>707</v>
-      </c>
-      <c r="AO59" s="13" t="s">
-        <v>708</v>
       </c>
       <c r="AP59" s="13" t="s">
         <v>115</v>
@@ -22642,7 +22645,7 @@
         <v>117</v>
       </c>
       <c r="AU59" s="13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AV59" s="13" t="s">
         <v>119</v>
@@ -22651,10 +22654,10 @@
         <v>800</v>
       </c>
       <c r="AX59" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="AY59" s="16" t="s">
         <v>710</v>
-      </c>
-      <c r="AY59" s="16" t="s">
-        <v>711</v>
       </c>
       <c r="AZ59" s="14">
         <v>46247</v>
@@ -22737,7 +22740,7 @@
         <v>127</v>
       </c>
       <c r="BX59" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="BY59" s="13" t="s">
         <v>124</v>
@@ -22810,13 +22813,13 @@
         <v>110</v>
       </c>
       <c r="CU59" s="13" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="CV59" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="60" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A60" s="12" t="s">
         <v>288</v>
       </c>
@@ -22831,7 +22834,7 @@
         <v>97</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F60" s="14">
         <v>46264</v>
@@ -22900,7 +22903,7 @@
         <v>46191</v>
       </c>
       <c r="AA60" s="13" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AB60" s="13">
         <v>24.51</v>
@@ -22933,7 +22936,7 @@
         <v>24510</v>
       </c>
       <c r="AL60" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AM60" s="13" t="s">
         <v>112</v>
@@ -22942,7 +22945,7 @@
         <v>20470</v>
       </c>
       <c r="AO60" s="16" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AP60" s="13" t="s">
         <v>115</v>
@@ -22969,7 +22972,7 @@
         <v>800</v>
       </c>
       <c r="AX60" s="13" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AY60" s="13">
         <v>9000102364</v>
@@ -23055,7 +23058,7 @@
         <v>127</v>
       </c>
       <c r="BX60" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="BY60" s="13" t="s">
         <v>124</v>
@@ -23127,13 +23130,13 @@
         <v>110</v>
       </c>
       <c r="CU60" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="CV60" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="61" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="61" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A61" s="12" t="s">
         <v>288</v>
       </c>
@@ -23218,7 +23221,7 @@
         <v>46197</v>
       </c>
       <c r="AA61" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AB61" s="13">
         <v>25.14</v>
@@ -23260,7 +23263,7 @@
         <v>20434</v>
       </c>
       <c r="AO61" s="16" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AP61" s="13" t="s">
         <v>115</v>
@@ -23278,7 +23281,7 @@
         <v>117</v>
       </c>
       <c r="AU61" s="13" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AV61" s="13" t="s">
         <v>119</v>
@@ -23287,7 +23290,7 @@
         <v>800</v>
       </c>
       <c r="AX61" s="13" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AY61" s="13">
         <v>9000102320</v>
@@ -23445,13 +23448,13 @@
         <v>110</v>
       </c>
       <c r="CU61" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="CV61" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="62" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="62" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A62" s="12" t="s">
         <v>288</v>
       </c>
@@ -23504,10 +23507,10 @@
         <v>102</v>
       </c>
       <c r="Q62" s="39" t="s">
+        <v>724</v>
+      </c>
+      <c r="R62" s="42" t="s">
         <v>725</v>
-      </c>
-      <c r="R62" s="42" t="s">
-        <v>726</v>
       </c>
       <c r="S62" s="13" t="s">
         <v>274</v>
@@ -23530,19 +23533,19 @@
         <v>183750</v>
       </c>
       <c r="Y62" s="19" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="Z62" s="14">
         <v>46202</v>
       </c>
       <c r="AA62" s="13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AB62" s="13">
         <v>25.27</v>
       </c>
       <c r="AC62" s="13" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AD62" s="13">
         <v>25.55</v>
@@ -23569,16 +23572,16 @@
         <v>25270</v>
       </c>
       <c r="AL62" s="16" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AM62" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN62" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="AO62" s="13" t="s">
         <v>731</v>
-      </c>
-      <c r="AO62" s="13" t="s">
-        <v>732</v>
       </c>
       <c r="AP62" s="13" t="s">
         <v>115</v>
@@ -23596,7 +23599,7 @@
         <v>117</v>
       </c>
       <c r="AU62" s="13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AV62" s="13" t="s">
         <v>119</v>
@@ -23605,10 +23608,10 @@
         <v>800</v>
       </c>
       <c r="AX62" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="AY62" s="16" t="s">
         <v>734</v>
-      </c>
-      <c r="AY62" s="16" t="s">
-        <v>735</v>
       </c>
       <c r="AZ62" s="14">
         <v>46226</v>
@@ -23693,7 +23696,7 @@
         <v>127</v>
       </c>
       <c r="BX62" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="BY62" s="13" t="s">
         <v>124</v>
@@ -23769,10 +23772,10 @@
         <v>110</v>
       </c>
       <c r="CU62" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="63" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="63" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A63" s="12" t="s">
         <v>288</v>
       </c>
@@ -23825,10 +23828,10 @@
         <v>102</v>
       </c>
       <c r="Q63" s="39" t="s">
+        <v>724</v>
+      </c>
+      <c r="R63" s="42" t="s">
         <v>725</v>
-      </c>
-      <c r="R63" s="42" t="s">
-        <v>726</v>
       </c>
       <c r="S63" s="13" t="s">
         <v>274</v>
@@ -23857,7 +23860,7 @@
         <v>46202</v>
       </c>
       <c r="AA63" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AB63" s="45">
         <v>25.51</v>
@@ -23890,7 +23893,7 @@
         <v>25510</v>
       </c>
       <c r="AL63" s="16" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AM63" s="13" t="s">
         <v>112</v>
@@ -23899,7 +23902,7 @@
         <v>20499</v>
       </c>
       <c r="AO63" s="16" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AP63" s="13" t="s">
         <v>115</v>
@@ -23917,7 +23920,7 @@
         <v>117</v>
       </c>
       <c r="AU63" s="13" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AV63" s="13" t="s">
         <v>119</v>
@@ -23926,7 +23929,7 @@
         <v>800</v>
       </c>
       <c r="AX63" s="13" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AY63" s="13">
         <v>9000102778</v>
@@ -24087,10 +24090,10 @@
         <v>110</v>
       </c>
       <c r="CU63" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
-    <row r="64" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="64" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A64" s="12" t="s">
         <v>288</v>
       </c>
@@ -24114,8 +24117,8 @@
         <f t="shared" si="26"/>
         <v>46305</v>
       </c>
-      <c r="H64" s="13" t="s">
-        <v>573</v>
+      <c r="H64" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>172</v>
@@ -24141,10 +24144,10 @@
         <v>102</v>
       </c>
       <c r="Q64" s="39" t="s">
+        <v>724</v>
+      </c>
+      <c r="R64" s="42" t="s">
         <v>725</v>
-      </c>
-      <c r="R64" s="42" t="s">
-        <v>726</v>
       </c>
       <c r="S64" s="13" t="s">
         <v>274</v>
@@ -24173,7 +24176,7 @@
         <v>46202</v>
       </c>
       <c r="AA64" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AB64" s="13">
         <v>25.49</v>
@@ -24206,7 +24209,7 @@
         <v>25490</v>
       </c>
       <c r="AL64" s="16" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AM64" s="13" t="s">
         <v>112</v>
@@ -24215,7 +24218,7 @@
         <v>20498</v>
       </c>
       <c r="AO64" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AP64" s="13" t="s">
         <v>115</v>
@@ -24239,7 +24242,7 @@
         <v>800</v>
       </c>
       <c r="AX64" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="BA64" s="45">
         <v>25.49</v>
@@ -24295,7 +24298,7 @@
       </c>
       <c r="BQ64" s="24"/>
       <c r="BR64" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS64" s="13" t="s">
         <v>169</v>
@@ -24313,7 +24316,7 @@
         <v>127</v>
       </c>
       <c r="BX64" s="13" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="BY64" s="13" t="s">
         <v>124</v>
@@ -24371,7 +24374,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="65" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="65" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A65" s="12" t="s">
         <v>288</v>
       </c>
@@ -24385,7 +24388,7 @@
         <v>97</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F65" s="43">
         <v>46288</v>
@@ -24394,8 +24397,8 @@
         <f t="shared" si="26"/>
         <v>46301</v>
       </c>
-      <c r="H65" s="13" t="s">
-        <v>573</v>
+      <c r="H65" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>172</v>
@@ -24423,10 +24426,10 @@
         <v>102</v>
       </c>
       <c r="Q65" s="39" t="s">
+        <v>724</v>
+      </c>
+      <c r="R65" s="42" t="s">
         <v>725</v>
-      </c>
-      <c r="R65" s="42" t="s">
-        <v>726</v>
       </c>
       <c r="S65" s="13" t="s">
         <v>274</v>
@@ -24455,7 +24458,7 @@
         <v>46216</v>
       </c>
       <c r="AA65" s="13" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AB65" s="13">
         <v>25.61</v>
@@ -24464,7 +24467,7 @@
         <v>25610</v>
       </c>
       <c r="AL65" s="16" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AM65" s="13" t="s">
         <v>112</v>
@@ -24473,7 +24476,7 @@
         <v>20330</v>
       </c>
       <c r="AO65" s="13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AP65" s="13" t="s">
         <v>115</v>
@@ -24497,7 +24500,7 @@
         <v>800</v>
       </c>
       <c r="AX65" s="13" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AY65" s="13">
         <v>9000103528</v>
@@ -24540,7 +24543,7 @@
       <c r="BP65" s="24"/>
       <c r="BQ65" s="24"/>
       <c r="BR65" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS65" s="13" t="s">
         <v>169</v>
@@ -24549,7 +24552,7 @@
         <v>124</v>
       </c>
       <c r="BU65" s="16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BV65" s="16" t="s">
         <v>258</v>
@@ -24558,7 +24561,7 @@
         <v>127</v>
       </c>
       <c r="BX65" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="BY65" s="13" t="s">
         <v>124</v>
@@ -24591,7 +24594,7 @@
       <c r="CQ65" s="18"/>
       <c r="CR65" s="24"/>
     </row>
-    <row r="66" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="66" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A66" s="12" t="s">
         <v>288</v>
       </c>
@@ -24676,7 +24679,7 @@
         <v>46200</v>
       </c>
       <c r="AA66" s="13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AB66" s="13">
         <v>24.74</v>
@@ -24709,7 +24712,7 @@
         <v>24740</v>
       </c>
       <c r="AL66" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AM66" s="13" t="s">
         <v>112</v>
@@ -24718,7 +24721,7 @@
         <v>20495</v>
       </c>
       <c r="AO66" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AP66" s="13" t="s">
         <v>115</v>
@@ -24736,7 +24739,7 @@
         <v>117</v>
       </c>
       <c r="AU66" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AV66" s="13" t="s">
         <v>119</v>
@@ -24745,7 +24748,7 @@
         <v>800</v>
       </c>
       <c r="AX66" s="13" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AY66" s="13">
         <v>9000102321</v>
@@ -24831,7 +24834,7 @@
         <v>127</v>
       </c>
       <c r="BX66" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="BY66" s="13" t="s">
         <v>124</v>
@@ -24907,10 +24910,10 @@
         <v>110</v>
       </c>
       <c r="CU66" s="13" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
-    <row r="67" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="67" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A67" s="12" t="s">
         <v>288</v>
       </c>
@@ -24925,7 +24928,7 @@
         <v>97</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F67" s="14">
         <v>46288</v>
@@ -24935,7 +24938,7 @@
         <v>46301</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>172</v>
@@ -24963,13 +24966,13 @@
         <v>102</v>
       </c>
       <c r="Q67" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R67" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S67" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T67" s="24">
         <v>400</v>
@@ -24995,7 +24998,7 @@
         <v>46208</v>
       </c>
       <c r="AA67" s="13" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AB67" s="13">
         <v>25.14</v>
@@ -25028,7 +25031,7 @@
         <v>25140</v>
       </c>
       <c r="AL67" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AM67" s="13" t="s">
         <v>112</v>
@@ -25037,7 +25040,7 @@
         <v>20370</v>
       </c>
       <c r="AO67" s="13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AP67" s="13" t="s">
         <v>115</v>
@@ -25055,7 +25058,7 @@
         <v>117</v>
       </c>
       <c r="AU67" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AV67" s="16" t="s">
         <v>119</v>
@@ -25064,7 +25067,7 @@
         <v>1600</v>
       </c>
       <c r="AX67" s="16" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AY67" s="13">
         <v>9000102542</v>
@@ -25126,7 +25129,7 @@
       </c>
       <c r="BQ67" s="24"/>
       <c r="BR67" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS67" s="13" t="s">
         <v>169</v>
@@ -25135,7 +25138,7 @@
         <v>124</v>
       </c>
       <c r="BU67" s="16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BV67" s="16" t="s">
         <v>258</v>
@@ -25144,7 +25147,7 @@
         <v>127</v>
       </c>
       <c r="BX67" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="BY67" s="13" t="s">
         <v>124</v>
@@ -25198,7 +25201,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="68" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="68" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A68" s="12" t="s">
         <v>288</v>
       </c>
@@ -25251,13 +25254,13 @@
         <v>102</v>
       </c>
       <c r="Q68" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R68" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S68" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T68" s="24">
         <v>400</v>
@@ -25283,7 +25286,7 @@
         <v>46199</v>
       </c>
       <c r="AA68" s="13" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AB68" s="13">
         <v>23.58</v>
@@ -25316,7 +25319,7 @@
         <v>23580</v>
       </c>
       <c r="AL68" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AM68" s="13" t="s">
         <v>112</v>
@@ -25325,7 +25328,7 @@
         <v>20408</v>
       </c>
       <c r="AO68" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AP68" s="13" t="s">
         <v>115</v>
@@ -25343,7 +25346,7 @@
         <v>117</v>
       </c>
       <c r="AU68" s="13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AV68" s="13" t="s">
         <v>119</v>
@@ -25352,7 +25355,7 @@
         <v>800</v>
       </c>
       <c r="AX68" s="13" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AY68" s="13">
         <v>9000102315</v>
@@ -25438,7 +25441,7 @@
         <v>127</v>
       </c>
       <c r="BX68" s="13" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="BY68" s="13" t="s">
         <v>124</v>
@@ -25511,13 +25514,13 @@
         <v>110</v>
       </c>
       <c r="CU68" s="13" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="CV68" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="69" spans="1:100" s="13" customFormat="1" ht="57.6">
       <c r="A69" s="12" t="s">
         <v>288</v>
       </c>
@@ -25532,7 +25535,7 @@
         <v>97</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F69" s="14">
         <v>46264</v>
@@ -25570,13 +25573,13 @@
         <v>102</v>
       </c>
       <c r="Q69" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R69" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S69" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T69" s="24">
         <v>400</v>
@@ -25596,19 +25599,19 @@
         <v>306000</v>
       </c>
       <c r="Y69" s="19" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="Z69" s="14">
         <v>46198</v>
       </c>
       <c r="AA69" s="13" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AB69" s="13">
         <v>24.76</v>
       </c>
       <c r="AC69" s="13" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AD69" s="13">
         <v>24.77</v>
@@ -25635,16 +25638,16 @@
         <v>24760</v>
       </c>
       <c r="AL69" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AM69" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN69" s="16" t="s">
+        <v>773</v>
+      </c>
+      <c r="AO69" s="16" t="s">
         <v>774</v>
-      </c>
-      <c r="AO69" s="16" t="s">
-        <v>775</v>
       </c>
       <c r="AP69" s="13" t="s">
         <v>115</v>
@@ -25662,7 +25665,7 @@
         <v>117</v>
       </c>
       <c r="AU69" s="13" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AV69" s="13" t="s">
         <v>119</v>
@@ -25671,10 +25674,10 @@
         <v>1600</v>
       </c>
       <c r="AX69" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="AY69" s="16" t="s">
         <v>777</v>
-      </c>
-      <c r="AY69" s="16" t="s">
-        <v>778</v>
       </c>
       <c r="AZ69" s="14">
         <v>46253</v>
@@ -25757,7 +25760,7 @@
         <v>127</v>
       </c>
       <c r="BX69" s="13" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="BY69" s="13" t="s">
         <v>124</v>
@@ -25781,7 +25784,7 @@
         <v>124</v>
       </c>
       <c r="CF69" s="13" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="CG69" s="13">
         <v>3423673</v>
@@ -25829,13 +25832,13 @@
         <v>211</v>
       </c>
       <c r="CU69" s="13" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="CV69" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="70" spans="1:100" s="13" customFormat="1" ht="57.6">
       <c r="A70" s="12" t="s">
         <v>288</v>
       </c>
@@ -25850,7 +25853,7 @@
         <v>97</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="F70" s="14">
         <v>46264</v>
@@ -25888,13 +25891,13 @@
         <v>102</v>
       </c>
       <c r="Q70" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R70" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S70" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T70" s="24">
         <v>400</v>
@@ -25914,19 +25917,19 @@
         <v>306000</v>
       </c>
       <c r="Y70" s="16" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="Z70" s="14">
         <v>46198</v>
       </c>
       <c r="AA70" s="13" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AB70" s="13">
         <v>25.1</v>
       </c>
       <c r="AC70" s="16" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AD70" s="16">
         <v>24.75</v>
@@ -25953,16 +25956,16 @@
         <v>25100</v>
       </c>
       <c r="AL70" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AM70" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN70" s="16" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AO70" s="16" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AP70" s="13" t="s">
         <v>115</v>
@@ -25980,7 +25983,7 @@
         <v>117</v>
       </c>
       <c r="AU70" s="13" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AV70" s="13" t="s">
         <v>119</v>
@@ -25989,10 +25992,10 @@
         <v>800</v>
       </c>
       <c r="AX70" s="13" t="s">
+        <v>787</v>
+      </c>
+      <c r="AY70" s="16" t="s">
         <v>788</v>
-      </c>
-      <c r="AY70" s="16" t="s">
-        <v>789</v>
       </c>
       <c r="AZ70" s="14">
         <v>46253</v>
@@ -26097,7 +26100,7 @@
         <v>124</v>
       </c>
       <c r="CF70" s="13" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="CG70" s="13">
         <v>3420994</v>
@@ -26148,10 +26151,10 @@
         <v>110</v>
       </c>
       <c r="CU70" s="13" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
-    <row r="71" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="71" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A71" s="12" t="s">
         <v>288</v>
       </c>
@@ -26166,7 +26169,7 @@
         <v>97</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F71" s="14">
         <v>46288</v>
@@ -26176,7 +26179,7 @@
         <v>46301</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>172</v>
@@ -26204,13 +26207,13 @@
         <v>102</v>
       </c>
       <c r="Q71" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R71" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S71" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T71" s="24">
         <v>400</v>
@@ -26236,7 +26239,7 @@
         <v>46198</v>
       </c>
       <c r="AA71" s="13" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AB71" s="13">
         <v>24.79</v>
@@ -26269,7 +26272,7 @@
         <v>24790</v>
       </c>
       <c r="AL71" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AM71" s="13" t="s">
         <v>112</v>
@@ -26278,7 +26281,7 @@
         <v>20395</v>
       </c>
       <c r="AO71" s="13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AP71" s="13" t="s">
         <v>115</v>
@@ -26296,7 +26299,7 @@
         <v>117</v>
       </c>
       <c r="AU71" s="13" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AV71" s="16" t="s">
         <v>119</v>
@@ -26305,7 +26308,7 @@
         <v>800</v>
       </c>
       <c r="AX71" s="13" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AY71" s="13">
         <v>9000103032</v>
@@ -26367,7 +26370,7 @@
       </c>
       <c r="BQ71" s="24"/>
       <c r="BR71" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS71" s="13" t="s">
         <v>169</v>
@@ -26376,7 +26379,7 @@
         <v>124</v>
       </c>
       <c r="BU71" s="16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BV71" s="16" t="s">
         <v>258</v>
@@ -26385,7 +26388,7 @@
         <v>127</v>
       </c>
       <c r="BX71" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="BY71" s="13" t="s">
         <v>124</v>
@@ -26439,7 +26442,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="72" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="72" spans="1:100" s="13" customFormat="1" ht="72">
       <c r="A72" s="12" t="s">
         <v>288</v>
       </c>
@@ -26454,7 +26457,7 @@
         <v>97</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F72" s="14">
         <v>46264</v>
@@ -26492,13 +26495,13 @@
         <v>102</v>
       </c>
       <c r="Q72" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R72" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S72" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T72" s="24">
         <v>400</v>
@@ -26518,25 +26521,25 @@
         <v>306000</v>
       </c>
       <c r="Y72" s="19" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Z72" s="14">
         <v>46198</v>
       </c>
       <c r="AA72" s="13" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AB72" s="13">
         <v>25.44</v>
       </c>
       <c r="AC72" s="13" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AD72" s="13">
         <v>24.92</v>
       </c>
       <c r="AE72" s="13" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AF72" s="13">
         <v>24.84</v>
@@ -26557,16 +26560,16 @@
         <v>75200</v>
       </c>
       <c r="AL72" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AM72" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN72" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="AO72" s="16" t="s">
         <v>799</v>
-      </c>
-      <c r="AO72" s="16" t="s">
-        <v>800</v>
       </c>
       <c r="AP72" s="13" t="s">
         <v>115</v>
@@ -26584,7 +26587,7 @@
         <v>117</v>
       </c>
       <c r="AU72" s="13" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AV72" s="13" t="s">
         <v>119</v>
@@ -26593,10 +26596,10 @@
         <v>800</v>
       </c>
       <c r="AX72" s="13" t="s">
+        <v>801</v>
+      </c>
+      <c r="AY72" s="16" t="s">
         <v>802</v>
-      </c>
-      <c r="AY72" s="16" t="s">
-        <v>803</v>
       </c>
       <c r="AZ72" s="14">
         <v>46253</v>
@@ -26679,7 +26682,7 @@
         <v>127</v>
       </c>
       <c r="BX72" s="13" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="BY72" s="13" t="s">
         <v>124</v>
@@ -26703,7 +26706,7 @@
         <v>124</v>
       </c>
       <c r="CF72" s="13" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="CG72" s="13">
         <v>3571957</v>
@@ -26751,13 +26754,13 @@
         <v>110</v>
       </c>
       <c r="CU72" s="13" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="CV72" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="73" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A73" s="12" t="s">
         <v>288</v>
       </c>
@@ -26772,7 +26775,7 @@
         <v>97</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F73" s="14">
         <v>46298</v>
@@ -26782,7 +26785,7 @@
         <v>46311</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>172</v>
@@ -26810,13 +26813,13 @@
         <v>102</v>
       </c>
       <c r="Q73" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R73" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S73" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T73" s="24">
         <v>400</v>
@@ -26842,7 +26845,7 @@
         <v>46226</v>
       </c>
       <c r="AA73" s="13" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AB73" s="13">
         <v>24.68</v>
@@ -26875,7 +26878,7 @@
         <v>24680</v>
       </c>
       <c r="AL73" s="13" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AM73" s="13" t="s">
         <v>112</v>
@@ -26884,7 +26887,7 @@
         <v>20282</v>
       </c>
       <c r="AO73" s="13" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AP73" s="13" t="s">
         <v>115</v>
@@ -26908,7 +26911,7 @@
         <v>800</v>
       </c>
       <c r="AX73" s="13" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AY73" s="13">
         <v>9000103914</v>
@@ -26970,7 +26973,7 @@
       </c>
       <c r="BQ73" s="24"/>
       <c r="BR73" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS73" s="13" t="s">
         <v>169</v>
@@ -26979,7 +26982,7 @@
         <v>124</v>
       </c>
       <c r="BU73" s="16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BV73" s="13" t="s">
         <v>354</v>
@@ -27039,7 +27042,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="74" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="74" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A74" s="12" t="s">
         <v>288</v>
       </c>
@@ -27054,7 +27057,7 @@
         <v>97</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F74" s="14">
         <v>46298</v>
@@ -27064,7 +27067,7 @@
         <v>46311</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>172</v>
@@ -27092,13 +27095,13 @@
         <v>102</v>
       </c>
       <c r="Q74" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R74" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S74" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T74" s="24">
         <v>400</v>
@@ -27124,7 +27127,7 @@
         <v>46219</v>
       </c>
       <c r="AA74" s="13" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AB74" s="13">
         <v>24.74</v>
@@ -27157,7 +27160,7 @@
         <v>24740</v>
       </c>
       <c r="AL74" s="16" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AM74" s="13" t="s">
         <v>112</v>
@@ -27166,7 +27169,7 @@
         <v>20267</v>
       </c>
       <c r="AO74" s="13" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AP74" s="13" t="s">
         <v>115</v>
@@ -27190,7 +27193,7 @@
         <v>800</v>
       </c>
       <c r="AX74" s="13" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AY74" s="13">
         <v>9000103543</v>
@@ -27252,7 +27255,7 @@
       </c>
       <c r="BQ74" s="24"/>
       <c r="BR74" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS74" s="13" t="s">
         <v>169</v>
@@ -27261,7 +27264,7 @@
         <v>124</v>
       </c>
       <c r="BU74" s="16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BV74" s="16" t="s">
         <v>258</v>
@@ -27321,7 +27324,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="75" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="75" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A75" s="12" t="s">
         <v>288</v>
       </c>
@@ -27346,7 +27349,7 @@
         <v>46293</v>
       </c>
       <c r="H75" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>100</v>
@@ -27374,13 +27377,13 @@
         <v>102</v>
       </c>
       <c r="Q75" s="39" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R75" s="42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S75" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T75" s="24">
         <v>400</v>
@@ -27400,19 +27403,19 @@
         <v>306000</v>
       </c>
       <c r="Y75" s="19" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Z75" s="14">
         <v>46198</v>
       </c>
       <c r="AA75" s="13" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AB75" s="13">
         <v>25.13</v>
       </c>
       <c r="AC75" s="13" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="AD75" s="13">
         <v>24.71</v>
@@ -27439,16 +27442,16 @@
         <v>49840</v>
       </c>
       <c r="AL75" s="13" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AM75" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN75" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="AO75" s="13" t="s">
         <v>819</v>
-      </c>
-      <c r="AO75" s="13" t="s">
-        <v>820</v>
       </c>
       <c r="AP75" s="13" t="s">
         <v>115</v>
@@ -27466,7 +27469,7 @@
         <v>117</v>
       </c>
       <c r="AU75" s="13" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AV75" s="16" t="s">
         <v>119</v>
@@ -27475,10 +27478,10 @@
         <v>800</v>
       </c>
       <c r="AX75" s="13" t="s">
+        <v>821</v>
+      </c>
+      <c r="AY75" s="16" t="s">
         <v>822</v>
-      </c>
-      <c r="AY75" s="16" t="s">
-        <v>823</v>
       </c>
       <c r="AZ75" s="14">
         <v>46266</v>
@@ -27626,10 +27629,10 @@
         <v>110</v>
       </c>
       <c r="CU75" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
-    <row r="76" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="76" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A76" s="12" t="s">
         <v>288</v>
       </c>
@@ -27681,13 +27684,13 @@
         <v>102</v>
       </c>
       <c r="Q76" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="R76" s="13" t="s">
         <v>825</v>
       </c>
-      <c r="R76" s="13" t="s">
+      <c r="S76" s="13" t="s">
         <v>826</v>
-      </c>
-      <c r="S76" s="13" t="s">
-        <v>827</v>
       </c>
       <c r="T76" s="24">
         <v>22</v>
@@ -27713,7 +27716,7 @@
         <v>46210</v>
       </c>
       <c r="AA76" s="13" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AB76" s="13">
         <v>24.19</v>
@@ -27746,16 +27749,16 @@
         <v>24190</v>
       </c>
       <c r="AL76" s="13" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AM76" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN76" s="47" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AO76" s="16" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AP76" s="13" t="s">
         <v>115</v>
@@ -27773,7 +27776,7 @@
         <v>117</v>
       </c>
       <c r="AU76" s="13" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AV76" s="13" t="s">
         <v>119</v>
@@ -27782,7 +27785,7 @@
         <v>800</v>
       </c>
       <c r="AX76" s="13" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AY76" s="13">
         <v>9000102812</v>
@@ -27862,7 +27865,7 @@
         <v>222</v>
       </c>
       <c r="BV76" s="13" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="BW76" s="16" t="s">
         <v>355</v>
@@ -27943,10 +27946,10 @@
         <v>110</v>
       </c>
       <c r="CU76" s="13" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
-    <row r="77" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="77" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A77" s="12" t="s">
         <v>288</v>
       </c>
@@ -27961,7 +27964,7 @@
         <v>97</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F77" s="14">
         <v>46122</v>
@@ -27971,7 +27974,7 @@
         <v>46135</v>
       </c>
       <c r="H77" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I77" s="15"/>
       <c r="J77" s="15"/>
@@ -27992,7 +27995,7 @@
         <v>102</v>
       </c>
       <c r="Q77" s="17" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="R77" s="13" t="s">
         <v>548</v>
@@ -28024,7 +28027,7 @@
         <v>46215</v>
       </c>
       <c r="AA77" s="13" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="AB77" s="41">
         <v>25.7</v>
@@ -28054,7 +28057,7 @@
         <v>110</v>
       </c>
       <c r="AL77" s="13" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AM77" s="13" t="s">
         <v>112</v>
@@ -28128,7 +28131,7 @@
       </c>
       <c r="BQ77" s="24"/>
       <c r="BR77" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS77" s="13" t="s">
         <v>169</v>
@@ -28197,7 +28200,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="78" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="78" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A78" s="12" t="s">
         <v>288</v>
       </c>
@@ -28213,7 +28216,7 @@
       </c>
       <c r="G78" s="14"/>
       <c r="H78" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I78" s="15"/>
       <c r="J78" s="15"/>
@@ -28232,10 +28235,10 @@
         <v>102</v>
       </c>
       <c r="Q78" s="17" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R78" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="S78" s="13" t="s">
         <v>274</v>
@@ -28354,7 +28357,7 @@
       </c>
       <c r="BQ78" s="24"/>
       <c r="BR78" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS78" s="13" t="s">
         <v>169</v>
@@ -28415,7 +28418,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="79" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="79" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A79" s="12" t="s">
         <v>288</v>
       </c>
@@ -28430,7 +28433,7 @@
         <v>97</v>
       </c>
       <c r="E79" s="32" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F79" s="14">
         <v>46122</v>
@@ -28440,7 +28443,7 @@
         <v>46135</v>
       </c>
       <c r="H79" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I79" s="15"/>
       <c r="J79" s="15"/>
@@ -28459,13 +28462,13 @@
         <v>102</v>
       </c>
       <c r="Q79" s="17" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="R79" s="13" t="s">
+        <v>825</v>
+      </c>
+      <c r="S79" s="13" t="s">
         <v>826</v>
-      </c>
-      <c r="S79" s="13" t="s">
-        <v>827</v>
       </c>
       <c r="T79" s="24">
         <v>22</v>
@@ -28491,7 +28494,7 @@
         <v>46224</v>
       </c>
       <c r="AA79" s="13" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AB79" s="41">
         <v>24.68</v>
@@ -28590,7 +28593,7 @@
       </c>
       <c r="BQ79" s="24"/>
       <c r="BR79" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS79" s="13" t="s">
         <v>169</v>
@@ -28659,7 +28662,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="80" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="80" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A80" s="12" t="s">
         <v>288</v>
       </c>
@@ -28675,7 +28678,7 @@
       </c>
       <c r="G80" s="14"/>
       <c r="H80" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I80" s="15"/>
       <c r="J80" s="15"/>
@@ -28694,10 +28697,10 @@
         <v>102</v>
       </c>
       <c r="Q80" s="17" t="s">
+        <v>842</v>
+      </c>
+      <c r="R80" s="13" t="s">
         <v>843</v>
-      </c>
-      <c r="R80" s="13" t="s">
-        <v>844</v>
       </c>
       <c r="S80" s="13" t="s">
         <v>305</v>
@@ -28726,7 +28729,7 @@
         <v>46229</v>
       </c>
       <c r="AA80" s="13" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AB80" s="41">
         <v>23.74</v>
@@ -28833,7 +28836,7 @@
       </c>
       <c r="BQ80" s="24"/>
       <c r="BR80" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS80" s="13" t="s">
         <v>169</v>
@@ -28894,7 +28897,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="81" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="81" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A81" s="12" t="s">
         <v>288</v>
       </c>
@@ -28910,7 +28913,7 @@
       </c>
       <c r="G81" s="14"/>
       <c r="H81" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I81" s="15"/>
       <c r="J81" s="15"/>
@@ -28929,10 +28932,10 @@
         <v>102</v>
       </c>
       <c r="Q81" s="17" t="s">
+        <v>845</v>
+      </c>
+      <c r="R81" s="13" t="s">
         <v>846</v>
-      </c>
-      <c r="R81" s="13" t="s">
-        <v>847</v>
       </c>
       <c r="S81" s="13" t="s">
         <v>373</v>
@@ -29045,7 +29048,7 @@
       </c>
       <c r="BQ81" s="24"/>
       <c r="BR81" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS81" s="13" t="s">
         <v>169</v>
@@ -29106,7 +29109,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="82" spans="1:100" s="13" customFormat="1" ht="409.6">
+    <row r="82" spans="1:100" s="13" customFormat="1" ht="86.4">
       <c r="A82" s="12" t="s">
         <v>288</v>
       </c>
@@ -29121,7 +29124,7 @@
         <v>97</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F82" s="14">
         <v>46138</v>
@@ -29153,19 +29156,19 @@
         <v>46165</v>
       </c>
       <c r="O82" s="30" t="s">
+        <v>848</v>
+      </c>
+      <c r="P82" s="13" t="s">
         <v>849</v>
       </c>
-      <c r="P82" s="13" t="s">
+      <c r="Q82" s="17" t="s">
         <v>850</v>
       </c>
-      <c r="Q82" s="17" t="s">
+      <c r="R82" s="19" t="s">
         <v>851</v>
       </c>
-      <c r="R82" s="19" t="s">
+      <c r="S82" s="16" t="s">
         <v>852</v>
-      </c>
-      <c r="S82" s="16" t="s">
-        <v>853</v>
       </c>
       <c r="T82" s="24">
         <v>21</v>
@@ -29192,7 +29195,7 @@
         <v>110</v>
       </c>
       <c r="AA82" s="13" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AB82" s="24">
         <v>23.756</v>
@@ -29234,7 +29237,7 @@
         <v>1020636</v>
       </c>
       <c r="AO82" s="13" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AP82" s="16" t="s">
         <v>425</v>
@@ -29252,7 +29255,7 @@
         <v>117</v>
       </c>
       <c r="AU82" s="13" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AV82" s="13" t="s">
         <v>119</v>
@@ -29261,10 +29264,10 @@
         <v>800</v>
       </c>
       <c r="AX82" s="13" t="s">
+        <v>856</v>
+      </c>
+      <c r="AY82" s="53" t="s">
         <v>857</v>
-      </c>
-      <c r="AY82" s="53" t="s">
-        <v>858</v>
       </c>
       <c r="AZ82" s="14">
         <v>46178</v>
@@ -29339,10 +29342,10 @@
         <v>124</v>
       </c>
       <c r="BU82" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="BV82" s="13" t="s">
         <v>859</v>
-      </c>
-      <c r="BV82" s="13" t="s">
-        <v>860</v>
       </c>
       <c r="BW82" s="16" t="s">
         <v>355</v>
@@ -29424,10 +29427,10 @@
         <v>110</v>
       </c>
       <c r="CU82" s="13" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
-    <row r="83" spans="1:100" s="13" customFormat="1" ht="409.6">
+    <row r="83" spans="1:100" s="13" customFormat="1" ht="86.4">
       <c r="A83" s="12" t="s">
         <v>288</v>
       </c>
@@ -29442,7 +29445,7 @@
         <v>97</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F83" s="43">
         <v>46215</v>
@@ -29464,7 +29467,7 @@
         <v>46193</v>
       </c>
       <c r="L83" s="13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="M83" s="13">
         <f t="shared" si="31"/>
@@ -29474,19 +29477,19 @@
         <v>46191</v>
       </c>
       <c r="O83" s="30" t="s">
+        <v>863</v>
+      </c>
+      <c r="P83" s="13" t="s">
         <v>864</v>
       </c>
-      <c r="P83" s="13" t="s">
+      <c r="Q83" s="17" t="s">
         <v>865</v>
       </c>
-      <c r="Q83" s="17" t="s">
+      <c r="R83" s="16" t="s">
         <v>866</v>
       </c>
-      <c r="R83" s="16" t="s">
+      <c r="S83" s="16" t="s">
         <v>867</v>
-      </c>
-      <c r="S83" s="16" t="s">
-        <v>868</v>
       </c>
       <c r="T83" s="24">
         <v>16.024000000000001</v>
@@ -29512,7 +29515,7 @@
         <v>110</v>
       </c>
       <c r="AA83" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AB83" s="24">
         <v>16.024000000000001</v>
@@ -29554,10 +29557,10 @@
         <v>1133000</v>
       </c>
       <c r="AO83" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="AP83" s="13" t="s">
         <v>870</v>
-      </c>
-      <c r="AP83" s="13" t="s">
-        <v>871</v>
       </c>
       <c r="AQ83" s="13" t="s">
         <v>116</v>
@@ -29569,7 +29572,7 @@
         <v>166</v>
       </c>
       <c r="AU83" s="13" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AV83" s="13" t="s">
         <v>119</v>
@@ -29578,10 +29581,10 @@
         <v>800</v>
       </c>
       <c r="AX83" s="13" t="s">
+        <v>872</v>
+      </c>
+      <c r="AY83" s="13" t="s">
         <v>873</v>
-      </c>
-      <c r="AY83" s="13" t="s">
-        <v>874</v>
       </c>
       <c r="AZ83" s="14">
         <v>46193</v>
@@ -29652,7 +29655,7 @@
         <v>124</v>
       </c>
       <c r="BU83" s="13" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="BV83" s="13" t="s">
         <v>354</v>
@@ -29737,10 +29740,10 @@
         <v>110</v>
       </c>
       <c r="CU83" s="13" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
-    <row r="84" spans="1:100" s="13" customFormat="1" ht="86.4">
+    <row r="84" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A84" s="12" t="s">
         <v>288</v>
       </c>
@@ -29755,7 +29758,7 @@
         <v>97</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F84" s="43">
         <v>46191</v>
@@ -29777,7 +29780,7 @@
         <v>46209</v>
       </c>
       <c r="L84" s="13" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="M84" s="13">
         <f t="shared" si="31"/>
@@ -29787,19 +29790,19 @@
         <v>46195</v>
       </c>
       <c r="O84" s="30" t="s">
+        <v>878</v>
+      </c>
+      <c r="P84" s="16" t="s">
         <v>879</v>
       </c>
-      <c r="P84" s="16" t="s">
+      <c r="Q84" s="17" t="s">
         <v>880</v>
       </c>
-      <c r="Q84" s="17" t="s">
+      <c r="R84" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="S84" s="16" t="s">
         <v>881</v>
-      </c>
-      <c r="R84" s="13" t="s">
-        <v>881</v>
-      </c>
-      <c r="S84" s="16" t="s">
-        <v>882</v>
       </c>
       <c r="T84" s="24">
         <v>25</v>
@@ -29825,7 +29828,7 @@
         <v>110</v>
       </c>
       <c r="AA84" s="13" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="AB84" s="13">
         <v>25.61</v>
@@ -29864,13 +29867,13 @@
         <v>112</v>
       </c>
       <c r="AN84" s="16" t="s">
+        <v>883</v>
+      </c>
+      <c r="AO84" s="16" t="s">
         <v>884</v>
       </c>
-      <c r="AO84" s="16" t="s">
+      <c r="AP84" s="13" t="s">
         <v>885</v>
-      </c>
-      <c r="AP84" s="13" t="s">
-        <v>886</v>
       </c>
       <c r="AQ84" s="13" t="s">
         <v>116</v>
@@ -29882,7 +29885,7 @@
         <v>72044900</v>
       </c>
       <c r="AU84" s="13" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="AV84" s="13" t="s">
         <v>119</v>
@@ -29891,10 +29894,10 @@
         <v>800</v>
       </c>
       <c r="AX84" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="AY84" s="13" t="s">
         <v>888</v>
-      </c>
-      <c r="AY84" s="13" t="s">
-        <v>889</v>
       </c>
       <c r="AZ84" s="14">
         <v>46198</v>
@@ -29968,7 +29971,7 @@
         <v>124</v>
       </c>
       <c r="BU84" s="13" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="BV84" s="13" t="s">
         <v>258</v>
@@ -29977,7 +29980,7 @@
         <v>127</v>
       </c>
       <c r="BX84" s="13" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="BY84" s="13" t="s">
         <v>380</v>
@@ -30053,13 +30056,13 @@
         <v>110</v>
       </c>
       <c r="CU84" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="CV84" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:100" s="13" customFormat="1" ht="115.2">
+    <row r="85" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A85" s="12" t="s">
         <v>288</v>
       </c>
@@ -30074,7 +30077,7 @@
         <v>97</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F85" s="14">
         <v>46226</v>
@@ -30106,16 +30109,16 @@
         <v>46153</v>
       </c>
       <c r="O85" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P85" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q85" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="R85" s="13" t="s">
         <v>895</v>
-      </c>
-      <c r="R85" s="13" t="s">
-        <v>896</v>
       </c>
       <c r="S85" s="13" t="s">
         <v>228</v>
@@ -30144,7 +30147,7 @@
         <v>46174</v>
       </c>
       <c r="AA85" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="AB85" s="24">
         <v>23.347999999999999</v>
@@ -30183,7 +30186,7 @@
         <v>112</v>
       </c>
       <c r="AN85" s="47" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="AO85" s="16" t="s">
         <v>512</v>
@@ -30204,7 +30207,7 @@
         <v>117</v>
       </c>
       <c r="AU85" s="13" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="AV85" s="13" t="s">
         <v>119</v>
@@ -30213,7 +30216,7 @@
         <v>800</v>
       </c>
       <c r="AX85" s="13" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AY85" s="13">
         <v>9000101155</v>
@@ -30263,7 +30266,7 @@
         <v>5775060.96</v>
       </c>
       <c r="BM85" s="41" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="BN85" s="24">
         <v>0</v>
@@ -30297,7 +30300,7 @@
         <v>127</v>
       </c>
       <c r="BX85" s="13" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="BY85" s="13" t="s">
         <v>380</v>
@@ -30372,10 +30375,10 @@
         <v>110</v>
       </c>
       <c r="CU85" s="13" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
-    <row r="86" spans="1:100" s="13" customFormat="1" ht="115.2">
+    <row r="86" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A86" s="12" t="s">
         <v>288</v>
       </c>
@@ -30390,7 +30393,7 @@
         <v>97</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F86" s="43">
         <v>46266</v>
@@ -30422,16 +30425,16 @@
         <v>46156</v>
       </c>
       <c r="O86" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P86" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q86" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="R86" s="13" t="s">
         <v>895</v>
-      </c>
-      <c r="R86" s="13" t="s">
-        <v>896</v>
       </c>
       <c r="S86" s="13" t="s">
         <v>228</v>
@@ -30460,7 +30463,7 @@
         <v>46176</v>
       </c>
       <c r="AA86" s="13" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="AB86" s="24">
         <v>21.251999999999999</v>
@@ -30493,16 +30496,16 @@
         <v>21252</v>
       </c>
       <c r="AL86" s="13" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AM86" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN86" s="47" t="s">
+        <v>906</v>
+      </c>
+      <c r="AO86" s="13" t="s">
         <v>907</v>
-      </c>
-      <c r="AO86" s="13" t="s">
-        <v>908</v>
       </c>
       <c r="AP86" s="13" t="s">
         <v>115</v>
@@ -30520,7 +30523,7 @@
         <v>117</v>
       </c>
       <c r="AU86" s="13" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AV86" s="13" t="s">
         <v>119</v>
@@ -30529,7 +30532,7 @@
         <v>1600</v>
       </c>
       <c r="AX86" s="16" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="AY86" s="13">
         <v>9000101552</v>
@@ -30612,7 +30615,7 @@
         <v>127</v>
       </c>
       <c r="BX86" s="13" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="BY86" s="13" t="s">
         <v>380</v>
@@ -30684,13 +30687,13 @@
         <v>110</v>
       </c>
       <c r="CU86" s="13" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="CV86" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="87" spans="1:100" s="13" customFormat="1" ht="115.2">
+    <row r="87" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A87" s="12" t="s">
         <v>288</v>
       </c>
@@ -30705,7 +30708,7 @@
         <v>97</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F87" s="43">
         <v>46292</v>
@@ -30715,7 +30718,7 @@
         <v>46305</v>
       </c>
       <c r="H87" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>172</v>
@@ -30735,16 +30738,16 @@
         <v>46156</v>
       </c>
       <c r="O87" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P87" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q87" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="R87" s="13" t="s">
         <v>895</v>
-      </c>
-      <c r="R87" s="13" t="s">
-        <v>896</v>
       </c>
       <c r="S87" s="13" t="s">
         <v>228</v>
@@ -30773,7 +30776,7 @@
         <v>46180</v>
       </c>
       <c r="AA87" s="13" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="AB87" s="24">
         <v>20.396000000000001</v>
@@ -30806,7 +30809,7 @@
         <v>20396</v>
       </c>
       <c r="AL87" s="13" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="AM87" s="13" t="s">
         <v>112</v>
@@ -30884,7 +30887,7 @@
       </c>
       <c r="BQ87" s="24"/>
       <c r="BR87" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS87" s="13" t="s">
         <v>169</v>
@@ -30956,7 +30959,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="88" spans="1:100" s="13" customFormat="1" ht="115.2">
+    <row r="88" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A88" s="12" t="s">
         <v>288</v>
       </c>
@@ -30971,7 +30974,7 @@
         <v>97</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F88" s="14">
         <v>46203</v>
@@ -31003,16 +31006,16 @@
         <v>46165</v>
       </c>
       <c r="O88" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P88" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q88" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="R88" s="13" t="s">
         <v>895</v>
-      </c>
-      <c r="R88" s="13" t="s">
-        <v>896</v>
       </c>
       <c r="S88" s="13" t="s">
         <v>228</v>
@@ -31041,7 +31044,7 @@
         <v>46175</v>
       </c>
       <c r="AA88" s="13" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="AB88" s="24">
         <v>21.25</v>
@@ -31080,10 +31083,10 @@
         <v>246</v>
       </c>
       <c r="AN88" s="16" t="s">
+        <v>916</v>
+      </c>
+      <c r="AO88" s="16" t="s">
         <v>917</v>
-      </c>
-      <c r="AO88" s="16" t="s">
-        <v>918</v>
       </c>
       <c r="AP88" s="13" t="s">
         <v>115</v>
@@ -31101,7 +31104,7 @@
         <v>117</v>
       </c>
       <c r="AU88" s="13" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AV88" s="13" t="s">
         <v>119</v>
@@ -31110,7 +31113,7 @@
         <v>800</v>
       </c>
       <c r="AX88" s="13" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="AY88" s="13">
         <v>9000101274</v>
@@ -31183,7 +31186,7 @@
         <v>124</v>
       </c>
       <c r="BU88" s="16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BV88" s="16" t="s">
         <v>258</v>
@@ -31192,7 +31195,7 @@
         <v>127</v>
       </c>
       <c r="BX88" s="13" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="BY88" s="13" t="s">
         <v>380</v>
@@ -31268,10 +31271,10 @@
         <v>110</v>
       </c>
       <c r="CU88" s="13" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
-    <row r="89" spans="1:100" s="13" customFormat="1" ht="100.8">
+    <row r="89" spans="1:100" s="13" customFormat="1" ht="57.6">
       <c r="A89" s="12" t="s">
         <v>288</v>
       </c>
@@ -31286,7 +31289,7 @@
         <v>97</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F89" s="14">
         <v>46234</v>
@@ -31318,19 +31321,19 @@
         <v>46165</v>
       </c>
       <c r="O89" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P89" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q89" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="R89" s="13" t="s">
         <v>923</v>
       </c>
-      <c r="R89" s="13" t="s">
+      <c r="S89" s="13" t="s">
         <v>924</v>
-      </c>
-      <c r="S89" s="13" t="s">
-        <v>925</v>
       </c>
       <c r="T89" s="24">
         <v>22</v>
@@ -31356,7 +31359,7 @@
         <v>46168</v>
       </c>
       <c r="AA89" s="13" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="AB89" s="24">
         <v>24.13</v>
@@ -31398,7 +31401,7 @@
         <v>33305</v>
       </c>
       <c r="AO89" s="16" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AP89" s="13" t="s">
         <v>115</v>
@@ -31416,7 +31419,7 @@
         <v>117</v>
       </c>
       <c r="AU89" s="13" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AV89" s="13" t="s">
         <v>119</v>
@@ -31425,7 +31428,7 @@
         <v>800</v>
       </c>
       <c r="AX89" s="13" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AY89" s="13">
         <v>9000103112</v>
@@ -31500,7 +31503,7 @@
         <v>124</v>
       </c>
       <c r="BU89" s="13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="BV89" s="13" t="s">
         <v>258</v>
@@ -31509,7 +31512,7 @@
         <v>127</v>
       </c>
       <c r="BX89" s="13" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="BY89" s="13" t="s">
         <v>380</v>
@@ -31582,10 +31585,10 @@
         <v>110</v>
       </c>
       <c r="CV89" s="16" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
-    <row r="90" spans="1:100" s="13" customFormat="1" ht="100.8">
+    <row r="90" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A90" s="12" t="s">
         <v>288</v>
       </c>
@@ -31600,7 +31603,7 @@
         <v>97</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="F90" s="14">
         <v>46266</v>
@@ -31632,19 +31635,19 @@
         <v>46176</v>
       </c>
       <c r="O90" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P90" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q90" s="17" t="s">
+        <v>933</v>
+      </c>
+      <c r="R90" s="54" t="s">
+        <v>633</v>
+      </c>
+      <c r="S90" s="13" t="s">
         <v>934</v>
-      </c>
-      <c r="R90" s="54" t="s">
-        <v>634</v>
-      </c>
-      <c r="S90" s="13" t="s">
-        <v>935</v>
       </c>
       <c r="T90" s="24">
         <v>25</v>
@@ -31670,7 +31673,7 @@
         <v>46179</v>
       </c>
       <c r="AA90" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="AB90" s="24">
         <v>24.84</v>
@@ -31703,16 +31706,16 @@
         <v>24840</v>
       </c>
       <c r="AL90" s="13" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AM90" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN90" s="47" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AO90" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AP90" s="13" t="s">
         <v>115</v>
@@ -31730,7 +31733,7 @@
         <v>117</v>
       </c>
       <c r="AU90" s="13" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="AV90" s="13" t="s">
         <v>119</v>
@@ -31739,7 +31742,7 @@
         <v>800</v>
       </c>
       <c r="AX90" s="13" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="AY90" s="13">
         <v>9000101654</v>
@@ -31824,7 +31827,7 @@
         <v>127</v>
       </c>
       <c r="BX90" s="13" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="BY90" s="13" t="s">
         <v>380</v>
@@ -31896,13 +31899,13 @@
         <v>110</v>
       </c>
       <c r="CU90" s="13" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="CV90" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="91" spans="1:100" s="13" customFormat="1" ht="100.8">
+    <row r="91" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A91" s="12" t="s">
         <v>288</v>
       </c>
@@ -31921,7 +31924,7 @@
         <v>13</v>
       </c>
       <c r="H91" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I91" s="15"/>
       <c r="J91" s="15"/>
@@ -31940,7 +31943,7 @@
         <v>370</v>
       </c>
       <c r="Q91" s="17" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="T91" s="24">
         <v>25</v>
@@ -32056,7 +32059,7 @@
         <v>0</v>
       </c>
       <c r="BR91" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS91" s="13" t="s">
         <v>169</v>
@@ -32121,7 +32124,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="92" spans="1:100" s="13" customFormat="1" ht="86.4">
+    <row r="92" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A92" s="12" t="s">
         <v>288</v>
       </c>
@@ -32136,7 +32139,7 @@
         <v>97</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F92" s="14">
         <v>46264</v>
@@ -32168,16 +32171,16 @@
         <v>46184</v>
       </c>
       <c r="O92" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P92" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q92" s="17" t="s">
+        <v>943</v>
+      </c>
+      <c r="R92" s="13" t="s">
         <v>944</v>
-      </c>
-      <c r="R92" s="13" t="s">
-        <v>945</v>
       </c>
       <c r="T92" s="24">
         <v>25</v>
@@ -32203,7 +32206,7 @@
         <v>46193</v>
       </c>
       <c r="AA92" s="13" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="AB92" s="24">
         <v>25.756</v>
@@ -32236,16 +32239,16 @@
         <v>25760</v>
       </c>
       <c r="AL92" s="13" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="AM92" s="13" t="s">
         <v>112</v>
       </c>
       <c r="AN92" s="47" t="s">
+        <v>947</v>
+      </c>
+      <c r="AO92" s="16" t="s">
         <v>948</v>
-      </c>
-      <c r="AO92" s="16" t="s">
-        <v>949</v>
       </c>
       <c r="AP92" s="13" t="s">
         <v>115</v>
@@ -32263,7 +32266,7 @@
         <v>117</v>
       </c>
       <c r="AU92" s="13" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="AV92" s="13" t="s">
         <v>119</v>
@@ -32272,7 +32275,7 @@
         <v>1600</v>
       </c>
       <c r="AX92" s="16" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AY92" s="13">
         <v>9000103023</v>
@@ -32355,7 +32358,7 @@
         <v>127</v>
       </c>
       <c r="BX92" s="13" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="BY92" s="13" t="s">
         <v>380</v>
@@ -32379,7 +32382,7 @@
         <v>124</v>
       </c>
       <c r="CF92" s="13" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="CG92" s="13">
         <v>3572348</v>
@@ -32427,13 +32430,13 @@
         <v>110</v>
       </c>
       <c r="CU92" s="13" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="CV92" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="93" spans="1:100" s="13" customFormat="1" ht="86.4">
+    <row r="93" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A93" s="12" t="s">
         <v>288</v>
       </c>
@@ -32448,7 +32451,7 @@
         <v>97</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F93" s="14">
         <v>46329</v>
@@ -32458,7 +32461,7 @@
         <v>46342</v>
       </c>
       <c r="H93" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I93" s="15"/>
       <c r="J93" s="15"/>
@@ -32479,13 +32482,13 @@
         <v>370</v>
       </c>
       <c r="Q93" s="17" t="s">
+        <v>954</v>
+      </c>
+      <c r="R93" s="13" t="s">
         <v>955</v>
       </c>
-      <c r="R93" s="13" t="s">
+      <c r="S93" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="S93" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="T93" s="24">
         <v>22</v>
@@ -32511,7 +32514,7 @@
         <v>46219</v>
       </c>
       <c r="AA93" s="13" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="AB93" s="24">
         <v>24.66</v>
@@ -32544,7 +32547,7 @@
         <v>24660</v>
       </c>
       <c r="AL93" s="13" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AM93" s="13" t="s">
         <v>112</v>
@@ -32553,7 +32556,7 @@
         <v>20268</v>
       </c>
       <c r="AO93" s="13" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AP93" s="13" t="s">
         <v>115</v>
@@ -32623,7 +32626,7 @@
         <v>0</v>
       </c>
       <c r="BR93" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS93" s="13" t="s">
         <v>169</v>
@@ -32688,7 +32691,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="94" spans="1:100" s="13" customFormat="1" ht="100.8">
+    <row r="94" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A94" s="12" t="s">
         <v>288</v>
       </c>
@@ -32741,10 +32744,10 @@
         <v>370</v>
       </c>
       <c r="Q94" s="17" t="s">
+        <v>960</v>
+      </c>
+      <c r="R94" s="13" t="s">
         <v>961</v>
-      </c>
-      <c r="R94" s="13" t="s">
-        <v>962</v>
       </c>
       <c r="S94" s="13" t="s">
         <v>305</v>
@@ -32773,7 +32776,7 @@
         <v>46210</v>
       </c>
       <c r="AA94" s="13" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="AB94" s="13">
         <v>22.31</v>
@@ -32815,7 +32818,7 @@
         <v>33475</v>
       </c>
       <c r="AO94" s="16" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AP94" s="13" t="s">
         <v>115</v>
@@ -32833,7 +32836,7 @@
         <v>117</v>
       </c>
       <c r="AU94" s="13" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="AV94" s="13" t="s">
         <v>119</v>
@@ -32842,7 +32845,7 @@
         <v>800</v>
       </c>
       <c r="AX94" s="13" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="AY94" s="13">
         <v>9000102792</v>
@@ -32921,13 +32924,13 @@
         <v>222</v>
       </c>
       <c r="BV94" s="13" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="BW94" s="16" t="s">
         <v>127</v>
       </c>
       <c r="BX94" s="13" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="BY94" s="13" t="s">
         <v>380</v>
@@ -33003,10 +33006,10 @@
         <v>110</v>
       </c>
       <c r="CU94" s="13" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
-    <row r="95" spans="1:100" s="29" customFormat="1" ht="158.4">
+    <row r="95" spans="1:100" s="29" customFormat="1" ht="57.6">
       <c r="A95" s="12" t="s">
         <v>288</v>
       </c>
@@ -33021,7 +33024,7 @@
         <v>97</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F95" s="14">
         <v>46221</v>
@@ -33051,19 +33054,19 @@
         <v>110</v>
       </c>
       <c r="O95" s="16" t="s">
+        <v>969</v>
+      </c>
+      <c r="P95" s="16" t="s">
         <v>970</v>
       </c>
-      <c r="P95" s="16" t="s">
+      <c r="Q95" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="Q95" s="17" t="s">
+      <c r="R95" s="13" t="s">
         <v>972</v>
       </c>
-      <c r="R95" s="13" t="s">
+      <c r="S95" s="16" t="s">
         <v>973</v>
-      </c>
-      <c r="S95" s="16" t="s">
-        <v>974</v>
       </c>
       <c r="T95" s="24">
         <v>17.9575</v>
@@ -33089,7 +33092,7 @@
         <v>110</v>
       </c>
       <c r="AA95" s="13" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="AB95" s="24">
         <v>17.9575</v>
@@ -33128,26 +33131,26 @@
         <v>112</v>
       </c>
       <c r="AN95" s="47" t="s">
+        <v>975</v>
+      </c>
+      <c r="AO95" s="16" t="s">
         <v>976</v>
       </c>
-      <c r="AO95" s="16" t="s">
+      <c r="AP95" s="13" t="s">
         <v>977</v>
-      </c>
-      <c r="AP95" s="13" t="s">
-        <v>978</v>
       </c>
       <c r="AQ95" s="13" t="s">
         <v>165</v>
       </c>
       <c r="AR95" s="13" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AS95" s="13">
         <v>72044900</v>
       </c>
       <c r="AT95" s="13"/>
       <c r="AU95" s="13" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="AV95" s="13" t="s">
         <v>119</v>
@@ -33156,10 +33159,10 @@
         <v>800</v>
       </c>
       <c r="AX95" s="13" t="s">
+        <v>980</v>
+      </c>
+      <c r="AY95" s="13" t="s">
         <v>981</v>
-      </c>
-      <c r="AY95" s="13" t="s">
-        <v>982</v>
       </c>
       <c r="AZ95" s="14">
         <v>46164</v>
@@ -33227,13 +33230,13 @@
         <v>124</v>
       </c>
       <c r="BU95" s="13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="BV95" s="16" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BW95" s="16" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BX95" s="13" t="s">
         <v>124</v>
@@ -33313,10 +33316,10 @@
       </c>
       <c r="CU95" s="13"/>
       <c r="CV95" s="44" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
-    <row r="96" spans="1:100" s="13" customFormat="1" ht="86.4">
+    <row r="96" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A96" s="12" t="s">
         <v>288</v>
       </c>
@@ -33331,7 +33334,7 @@
         <v>97</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F96" s="14">
         <v>46226</v>
@@ -33353,7 +33356,7 @@
         <v>46209</v>
       </c>
       <c r="L96" s="13" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M96" s="13">
         <f t="shared" si="31"/>
@@ -33363,16 +33366,16 @@
         <v>46186</v>
       </c>
       <c r="O96" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="P96" s="13" t="s">
         <v>987</v>
       </c>
-      <c r="P96" s="13" t="s">
+      <c r="Q96" s="17" t="s">
         <v>988</v>
       </c>
-      <c r="Q96" s="17" t="s">
-        <v>989</v>
-      </c>
       <c r="R96" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="S96" s="13" t="s">
         <v>228</v>
@@ -33401,7 +33404,7 @@
         <v>110</v>
       </c>
       <c r="AA96" s="13" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="AB96" s="24">
         <v>24.31</v>
@@ -33461,7 +33464,7 @@
         <v>117</v>
       </c>
       <c r="AU96" s="13" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AV96" s="13" t="s">
         <v>119</v>
@@ -33471,10 +33474,10 @@
         <v>1600</v>
       </c>
       <c r="AX96" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="AY96" s="13" t="s">
         <v>992</v>
-      </c>
-      <c r="AY96" s="13" t="s">
-        <v>993</v>
       </c>
       <c r="AZ96" s="14">
         <v>46210</v>
@@ -33489,7 +33492,7 @@
         <v>0</v>
       </c>
       <c r="BD96" s="24" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="BE96" s="24">
         <f t="shared" si="36"/>
@@ -33633,10 +33636,10 @@
         <v>110</v>
       </c>
       <c r="CU96" s="13" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
-    <row r="97" spans="1:100" s="13" customFormat="1" ht="86.4">
+    <row r="97" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A97" s="12" t="s">
         <v>288</v>
       </c>
@@ -33651,7 +33654,7 @@
         <v>97</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F97" s="43">
         <v>46292</v>
@@ -33661,7 +33664,7 @@
         <v>46305</v>
       </c>
       <c r="H97" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I97" s="15" t="s">
         <v>172</v>
@@ -33670,7 +33673,7 @@
         <v>172</v>
       </c>
       <c r="L97" s="13" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M97" s="13">
         <f t="shared" si="31"/>
@@ -33680,16 +33683,16 @@
         <v>46186</v>
       </c>
       <c r="O97" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="P97" s="13" t="s">
         <v>987</v>
       </c>
-      <c r="P97" s="13" t="s">
+      <c r="Q97" s="17" t="s">
         <v>988</v>
       </c>
-      <c r="Q97" s="17" t="s">
-        <v>989</v>
-      </c>
       <c r="R97" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="S97" s="13" t="s">
         <v>228</v>
@@ -33718,7 +33721,7 @@
         <v>110</v>
       </c>
       <c r="AA97" s="13" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AB97" s="24">
         <v>25.41</v>
@@ -33760,7 +33763,7 @@
         <v>33341</v>
       </c>
       <c r="AO97" s="13" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="AP97" s="13" t="s">
         <v>115</v>
@@ -33784,10 +33787,10 @@
         <v>800</v>
       </c>
       <c r="AX97" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="AY97" s="13" t="s">
         <v>999</v>
-      </c>
-      <c r="AY97" s="13" t="s">
-        <v>1000</v>
       </c>
       <c r="AZ97" s="14">
         <v>46230</v>
@@ -33846,7 +33849,7 @@
       </c>
       <c r="BQ97" s="24"/>
       <c r="BR97" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS97" s="13" t="s">
         <v>169</v>
@@ -33919,7 +33922,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="98" spans="1:100" s="13" customFormat="1" ht="201.6">
+    <row r="98" spans="1:100" s="13" customFormat="1" ht="57.6">
       <c r="A98" s="12" t="s">
         <v>288</v>
       </c>
@@ -33934,7 +33937,7 @@
         <v>97</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F98" s="14">
         <v>46238</v>
@@ -33956,7 +33959,7 @@
         <v>46221</v>
       </c>
       <c r="L98" s="13" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M98" s="13">
         <f t="shared" si="31"/>
@@ -33966,19 +33969,19 @@
         <v>46195</v>
       </c>
       <c r="O98" s="16" t="s">
+        <v>986</v>
+      </c>
+      <c r="P98" s="13" t="s">
         <v>987</v>
       </c>
-      <c r="P98" s="13" t="s">
-        <v>988</v>
-      </c>
       <c r="Q98" s="17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="R98" s="16" t="s">
         <v>1003</v>
       </c>
-      <c r="R98" s="16" t="s">
+      <c r="S98" s="16" t="s">
         <v>1004</v>
-      </c>
-      <c r="S98" s="16" t="s">
-        <v>1005</v>
       </c>
       <c r="T98" s="24">
         <f>8+17</f>
@@ -34006,7 +34009,7 @@
         <v>110</v>
       </c>
       <c r="AA98" s="13" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AB98" s="24">
         <f>6.1+19.86</f>
@@ -34049,7 +34052,7 @@
         <v>26284</v>
       </c>
       <c r="AO98" s="16" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="AP98" s="13" t="s">
         <v>115</v>
@@ -34067,7 +34070,7 @@
         <v>117</v>
       </c>
       <c r="AU98" s="13" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AV98" s="13" t="s">
         <v>119</v>
@@ -34076,10 +34079,10 @@
         <v>800</v>
       </c>
       <c r="AX98" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AY98" s="13" t="s">
         <v>1009</v>
-      </c>
-      <c r="AY98" s="13" t="s">
-        <v>1010</v>
       </c>
       <c r="AZ98" s="14">
         <v>46218</v>
@@ -34158,7 +34161,7 @@
         <v>127</v>
       </c>
       <c r="BX98" s="13" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="BY98" s="13" t="s">
         <v>124</v>
@@ -34233,10 +34236,10 @@
         <v>110</v>
       </c>
       <c r="CV98" s="16" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
-    <row r="99" spans="1:100" s="13" customFormat="1" ht="409.6">
+    <row r="99" spans="1:100" s="13" customFormat="1" ht="72">
       <c r="A99" s="12" t="s">
         <v>288</v>
       </c>
@@ -34251,7 +34254,7 @@
         <v>97</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F99" s="14">
         <v>46189</v>
@@ -34273,7 +34276,7 @@
         <v>46183</v>
       </c>
       <c r="L99" s="13" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="M99" s="13">
         <f t="shared" si="31"/>
@@ -34283,19 +34286,19 @@
         <v>46160</v>
       </c>
       <c r="O99" s="30" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="P99" s="13" t="s">
         <v>393</v>
       </c>
       <c r="Q99" s="17" t="s">
+        <v>1015</v>
+      </c>
+      <c r="R99" s="16" t="s">
         <v>1016</v>
       </c>
-      <c r="R99" s="16" t="s">
+      <c r="S99" s="16" t="s">
         <v>1017</v>
-      </c>
-      <c r="S99" s="16" t="s">
-        <v>1018</v>
       </c>
       <c r="T99" s="24">
         <v>26.22</v>
@@ -34321,7 +34324,7 @@
         <v>110</v>
       </c>
       <c r="AA99" s="13" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="AB99" s="20">
         <f>T99</f>
@@ -34361,10 +34364,10 @@
         <v>112</v>
       </c>
       <c r="AN99" s="16" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AO99" s="16" t="s">
         <v>1020</v>
-      </c>
-      <c r="AO99" s="16" t="s">
-        <v>1021</v>
       </c>
       <c r="AP99" s="16" t="s">
         <v>425</v>
@@ -34379,7 +34382,7 @@
         <v>166</v>
       </c>
       <c r="AU99" s="13" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="AV99" s="13" t="s">
         <v>119</v>
@@ -34388,10 +34391,10 @@
         <v>800</v>
       </c>
       <c r="AX99" s="13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AY99" s="16" t="s">
         <v>1023</v>
-      </c>
-      <c r="AY99" s="16" t="s">
-        <v>1024</v>
       </c>
       <c r="AZ99" s="14">
         <v>46161</v>
@@ -34467,7 +34470,7 @@
         <v>124</v>
       </c>
       <c r="BU99" s="16" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="BV99" s="16" t="s">
         <v>354</v>
@@ -34552,10 +34555,10 @@
         <v>110</v>
       </c>
       <c r="CU99" s="13" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
-    <row r="100" spans="1:100" s="13" customFormat="1" ht="158.4">
+    <row r="100" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A100" s="55" t="s">
         <v>288</v>
       </c>
@@ -34567,10 +34570,10 @@
         <v>571</v>
       </c>
       <c r="D100" s="29" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E100" s="13" t="s">
         <v>1026</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>1027</v>
       </c>
       <c r="F100" s="14">
         <v>46188</v>
@@ -34580,7 +34583,7 @@
         <v>46201</v>
       </c>
       <c r="H100" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I100" s="15" t="s">
         <v>100</v>
@@ -34599,19 +34602,19 @@
         <v>110</v>
       </c>
       <c r="O100" s="16" t="s">
+        <v>969</v>
+      </c>
+      <c r="P100" s="16" t="s">
         <v>970</v>
       </c>
-      <c r="P100" s="16" t="s">
+      <c r="Q100" s="17" t="s">
         <v>971</v>
       </c>
-      <c r="Q100" s="17" t="s">
+      <c r="R100" s="13" t="s">
         <v>972</v>
       </c>
-      <c r="R100" s="13" t="s">
+      <c r="S100" s="16" t="s">
         <v>973</v>
-      </c>
-      <c r="S100" s="16" t="s">
-        <v>974</v>
       </c>
       <c r="T100" s="24">
         <v>19.5</v>
@@ -34637,7 +34640,7 @@
         <v>110</v>
       </c>
       <c r="AA100" s="13" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AB100" s="20">
         <v>19.5</v>
@@ -34673,25 +34676,25 @@
         <v>246</v>
       </c>
       <c r="AN100" s="47" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AO100" s="13" t="s">
         <v>1029</v>
       </c>
-      <c r="AO100" s="13" t="s">
-        <v>1030</v>
-      </c>
       <c r="AP100" s="16" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AQ100" s="13" t="s">
         <v>165</v>
       </c>
       <c r="AR100" s="16" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="AS100" s="13">
         <v>72042920</v>
       </c>
       <c r="AU100" s="13" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="AV100" s="16" t="s">
         <v>119</v>
@@ -34700,10 +34703,10 @@
         <v>800</v>
       </c>
       <c r="AX100" s="13" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AY100" s="16" t="s">
         <v>1033</v>
-      </c>
-      <c r="AY100" s="16" t="s">
-        <v>1034</v>
       </c>
       <c r="AZ100" s="14">
         <v>46175</v>
@@ -34770,11 +34773,11 @@
         <v>124</v>
       </c>
       <c r="BU100" s="16" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="BV100" s="16"/>
       <c r="BW100" s="16" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BX100" s="13" t="s">
         <v>124</v>
@@ -34848,7 +34851,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:100" s="13" customFormat="1" ht="360">
+    <row r="101" spans="1:100" s="13" customFormat="1" ht="86.4">
       <c r="A101" s="12" t="s">
         <v>288</v>
       </c>
@@ -34863,7 +34866,7 @@
         <v>97</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F101" s="14">
         <v>46289</v>
@@ -34873,7 +34876,7 @@
         <v>46302</v>
       </c>
       <c r="H101" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I101" s="15" t="s">
         <v>172</v>
@@ -34885,7 +34888,7 @@
         <v>46234</v>
       </c>
       <c r="L101" s="13" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="M101" s="13">
         <f t="shared" si="31"/>
@@ -34895,19 +34898,19 @@
         <v>46224</v>
       </c>
       <c r="O101" s="16" t="s">
+        <v>969</v>
+      </c>
+      <c r="P101" s="16" t="s">
         <v>970</v>
       </c>
-      <c r="P101" s="16" t="s">
-        <v>971</v>
-      </c>
       <c r="Q101" s="17" t="s">
+        <v>1037</v>
+      </c>
+      <c r="R101" s="56" t="s">
         <v>1038</v>
       </c>
-      <c r="R101" s="56" t="s">
+      <c r="S101" s="16" t="s">
         <v>1039</v>
-      </c>
-      <c r="S101" s="16" t="s">
-        <v>1040</v>
       </c>
       <c r="T101" s="24">
         <v>19.811</v>
@@ -34934,7 +34937,7 @@
         <v>110</v>
       </c>
       <c r="AA101" s="13" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AB101" s="20">
         <v>19.811</v>
@@ -34970,28 +34973,28 @@
         <v>246</v>
       </c>
       <c r="AN101" s="47" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AO101" s="13" t="s">
         <v>1042</v>
       </c>
-      <c r="AO101" s="13" t="s">
+      <c r="AP101" s="16" t="s">
         <v>1043</v>
-      </c>
-      <c r="AP101" s="16" t="s">
-        <v>1044</v>
       </c>
       <c r="AQ101" s="13" t="s">
         <v>165</v>
       </c>
       <c r="AR101" s="16" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AS101" s="13">
         <v>72042920</v>
       </c>
       <c r="AT101" s="45" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AU101" s="13" t="s">
         <v>1045</v>
-      </c>
-      <c r="AU101" s="13" t="s">
-        <v>1046</v>
       </c>
       <c r="AV101" s="16" t="s">
         <v>119</v>
@@ -35000,10 +35003,10 @@
         <v>800</v>
       </c>
       <c r="AX101" s="13" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AY101" s="16" t="s">
         <v>1047</v>
-      </c>
-      <c r="AY101" s="16" t="s">
-        <v>1048</v>
       </c>
       <c r="AZ101" s="14">
         <v>46227</v>
@@ -35062,7 +35065,7 @@
       </c>
       <c r="BQ101" s="24"/>
       <c r="BR101" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS101" s="13" t="s">
         <v>169</v>
@@ -35071,11 +35074,11 @@
         <v>124</v>
       </c>
       <c r="BU101" s="16" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="BV101" s="16"/>
       <c r="BW101" s="16" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BX101" s="13" t="s">
         <v>124</v>
@@ -35134,7 +35137,7 @@
       <c r="CR101" s="24"/>
       <c r="CS101" s="14"/>
     </row>
-    <row r="102" spans="1:100" s="13" customFormat="1" ht="316.8">
+    <row r="102" spans="1:100" s="13" customFormat="1" ht="57.6">
       <c r="A102" s="55" t="s">
         <v>288</v>
       </c>
@@ -35146,10 +35149,10 @@
         <v>571</v>
       </c>
       <c r="D102" s="29" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F102" s="14">
         <v>46244</v>
@@ -35159,7 +35162,7 @@
         <v>46257</v>
       </c>
       <c r="H102" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I102" s="15"/>
       <c r="J102" s="15"/>
@@ -35175,16 +35178,16 @@
       </c>
       <c r="O102" s="16"/>
       <c r="P102" s="16" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="Q102" s="17" t="s">
+        <v>1050</v>
+      </c>
+      <c r="R102" s="16" t="s">
         <v>1051</v>
       </c>
-      <c r="R102" s="16" t="s">
-        <v>1052</v>
-      </c>
       <c r="S102" s="16" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="T102" s="24">
         <v>18.771799999999999</v>
@@ -35211,7 +35214,7 @@
         <v>110</v>
       </c>
       <c r="AA102" s="13" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AB102" s="20">
         <v>18.771799999999999</v>
@@ -35247,34 +35250,34 @@
         <v>246</v>
       </c>
       <c r="AN102" s="47" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="AO102" s="13" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AP102" s="13" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="AQ102" s="13" t="s">
         <v>165</v>
       </c>
       <c r="AR102" s="16" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="AS102" s="13">
         <v>72042920</v>
       </c>
       <c r="AU102" s="13" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="AW102" s="24">
         <v>800</v>
       </c>
       <c r="AX102" s="13" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AY102" s="16" t="s">
         <v>1056</v>
-      </c>
-      <c r="AY102" s="16" t="s">
-        <v>1057</v>
       </c>
       <c r="AZ102" s="14">
         <v>46175</v>
@@ -35343,11 +35346,11 @@
         <v>124</v>
       </c>
       <c r="BU102" s="16" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="BV102" s="16"/>
       <c r="BW102" s="16" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BX102" s="13" t="s">
         <v>124</v>
@@ -35418,7 +35421,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="103" spans="1:100" s="13" customFormat="1" ht="144">
+    <row r="103" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A103" s="12" t="s">
         <v>95</v>
       </c>
@@ -35433,7 +35436,7 @@
         <v>97</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F103" s="14">
         <v>46149</v>
@@ -35471,13 +35474,13 @@
         <v>102</v>
       </c>
       <c r="Q103" s="17" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="R103" s="16" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="S103" s="16" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="T103" s="24">
         <v>100</v>
@@ -35503,7 +35506,7 @@
         <v>46167</v>
       </c>
       <c r="AA103" s="13" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="AB103" s="13">
         <v>25.22</v>
@@ -35536,7 +35539,7 @@
         <v>25222</v>
       </c>
       <c r="AL103" s="13" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AM103" s="13" t="s">
         <v>112</v>
@@ -35563,7 +35566,7 @@
         <v>117</v>
       </c>
       <c r="AU103" s="13" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AV103" s="13" t="s">
         <v>119</v>
@@ -35572,7 +35575,7 @@
         <v>800</v>
       </c>
       <c r="AX103" s="13" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AY103" s="16">
         <v>9000101153</v>
@@ -35734,10 +35737,10 @@
         <v>110</v>
       </c>
       <c r="CU103" s="13" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
-    <row r="104" spans="1:100" s="13" customFormat="1" ht="100.8">
+    <row r="104" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A104" s="12" t="s">
         <v>288</v>
       </c>
@@ -35752,7 +35755,7 @@
         <v>97</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F104" s="14">
         <v>46122</v>
@@ -35762,7 +35765,7 @@
         <v>46135</v>
       </c>
       <c r="H104" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I104" s="15"/>
       <c r="J104" s="15"/>
@@ -35781,13 +35784,13 @@
         <v>370</v>
       </c>
       <c r="Q104" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="R104" s="13" t="s">
         <v>825</v>
       </c>
-      <c r="R104" s="13" t="s">
+      <c r="S104" s="13" t="s">
         <v>826</v>
-      </c>
-      <c r="S104" s="13" t="s">
-        <v>827</v>
       </c>
       <c r="T104" s="24">
         <v>22</v>
@@ -35813,7 +35816,7 @@
         <v>46223</v>
       </c>
       <c r="AA104" s="13" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="AB104" s="24">
         <v>23.77</v>
@@ -35916,7 +35919,7 @@
         <v>0</v>
       </c>
       <c r="BR104" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS104" s="13" t="s">
         <v>169</v>
@@ -35984,7 +35987,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="105" spans="1:100" s="13" customFormat="1" ht="259.2">
+    <row r="105" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A105" s="12" t="s">
         <v>288</v>
       </c>
@@ -35999,7 +36002,7 @@
         <v>97</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F105" s="14">
         <v>46294</v>
@@ -36009,7 +36012,7 @@
         <v>46307</v>
       </c>
       <c r="H105" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I105" s="15"/>
       <c r="J105" s="15"/>
@@ -36024,19 +36027,19 @@
         <v>46210</v>
       </c>
       <c r="O105" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P105" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q105" s="17" t="s">
+        <v>1067</v>
+      </c>
+      <c r="R105" s="16" t="s">
         <v>1068</v>
       </c>
-      <c r="R105" s="16" t="s">
-        <v>1069</v>
-      </c>
       <c r="S105" s="16" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="T105" s="24">
         <f>16.318+1.874+6.674</f>
@@ -36064,7 +36067,7 @@
         <v>46218</v>
       </c>
       <c r="AA105" s="13" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="AB105" s="24">
         <f>16.318+1.874+6.674</f>
@@ -36171,7 +36174,7 @@
         <v>0</v>
       </c>
       <c r="BR105" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS105" s="13" t="s">
         <v>169</v>
@@ -36183,7 +36186,7 @@
         <v>299</v>
       </c>
       <c r="BV105" s="13" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="BW105" s="16" t="s">
         <v>127</v>
@@ -36241,7 +36244,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="106" spans="1:100" s="13" customFormat="1" ht="86.4">
+    <row r="106" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A106" s="12" t="s">
         <v>288</v>
       </c>
@@ -36259,7 +36262,7 @@
         <v>211</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I106" s="15"/>
       <c r="J106" s="15"/>
@@ -36278,13 +36281,13 @@
         <v>370</v>
       </c>
       <c r="Q106" s="17" t="s">
+        <v>1070</v>
+      </c>
+      <c r="R106" s="13" t="s">
         <v>1071</v>
       </c>
-      <c r="R106" s="13" t="s">
+      <c r="S106" s="13" t="s">
         <v>1072</v>
-      </c>
-      <c r="S106" s="13" t="s">
-        <v>1073</v>
       </c>
       <c r="T106" s="24">
         <v>22</v>
@@ -36310,7 +36313,7 @@
         <v>46230</v>
       </c>
       <c r="AA106" s="13" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="AB106" s="24">
         <v>20.52</v>
@@ -36399,7 +36402,7 @@
         <v>0</v>
       </c>
       <c r="BR106" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS106" s="13" t="s">
         <v>169</v>
@@ -36464,7 +36467,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="107" spans="1:100" s="13" customFormat="1" ht="302.39999999999998">
+    <row r="107" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A107" s="12" t="s">
         <v>288</v>
       </c>
@@ -36479,7 +36482,7 @@
         <v>97</v>
       </c>
       <c r="E107" s="57" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F107" s="14">
         <v>46298</v>
@@ -36489,7 +36492,7 @@
         <v>46311</v>
       </c>
       <c r="H107" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I107" s="15"/>
       <c r="J107" s="15"/>
@@ -36504,16 +36507,16 @@
         <v>46215</v>
       </c>
       <c r="O107" s="30" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P107" s="16" t="s">
         <v>370</v>
       </c>
       <c r="Q107" s="17" t="s">
+        <v>1075</v>
+      </c>
+      <c r="R107" s="16" t="s">
         <v>1076</v>
-      </c>
-      <c r="R107" s="16" t="s">
-        <v>1077</v>
       </c>
       <c r="T107" s="24">
         <v>23</v>
@@ -36571,16 +36574,16 @@
         <v>27802</v>
       </c>
       <c r="AO107" s="13" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AP107" s="13" t="s">
         <v>115</v>
       </c>
       <c r="AQ107" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR107" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS107" s="13">
         <v>72042190</v>
@@ -36589,7 +36592,7 @@
         <v>117</v>
       </c>
       <c r="AU107" s="13" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AV107" s="13" t="s">
         <v>119</v>
@@ -36598,13 +36601,13 @@
         <v>800</v>
       </c>
       <c r="AX107" s="13" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AY107" s="13">
         <v>9000103524</v>
       </c>
       <c r="AZ107" s="13" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="BA107" s="45">
         <v>23.687999999999999</v>
@@ -36659,7 +36662,7 @@
         <v>0</v>
       </c>
       <c r="BR107" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS107" s="13" t="s">
         <v>169</v>
@@ -36668,7 +36671,7 @@
         <v>124</v>
       </c>
       <c r="BU107" s="16" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BV107" s="13" t="s">
         <v>258</v>
@@ -36677,10 +36680,10 @@
         <v>127</v>
       </c>
       <c r="BX107" s="58" t="s">
+        <v>1081</v>
+      </c>
+      <c r="BY107" s="13" t="s">
         <v>1082</v>
-      </c>
-      <c r="BY107" s="13" t="s">
-        <v>1083</v>
       </c>
       <c r="BZ107" s="24"/>
       <c r="CA107" s="24"/>
@@ -36735,7 +36738,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="108" spans="1:100" s="13" customFormat="1" ht="259.2">
+    <row r="108" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A108" s="12" t="s">
         <v>288</v>
       </c>
@@ -36757,7 +36760,7 @@
         <v>13</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I108" s="15"/>
       <c r="J108" s="15"/>
@@ -36776,13 +36779,13 @@
         <v>370</v>
       </c>
       <c r="Q108" s="17" t="s">
+        <v>1083</v>
+      </c>
+      <c r="R108" s="16" t="s">
         <v>1084</v>
       </c>
-      <c r="R108" s="16" t="s">
+      <c r="S108" s="16" t="s">
         <v>1085</v>
-      </c>
-      <c r="S108" s="16" t="s">
-        <v>1086</v>
       </c>
       <c r="T108" s="24">
         <v>44</v>
@@ -36887,7 +36890,7 @@
         <v>0</v>
       </c>
       <c r="BR108" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS108" s="13" t="s">
         <v>169</v>
@@ -36941,7 +36944,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="109" spans="1:100" s="13" customFormat="1" ht="100.8">
+    <row r="109" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A109" s="12" t="s">
         <v>288</v>
       </c>
@@ -36960,7 +36963,7 @@
         <v>13</v>
       </c>
       <c r="H109" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I109" s="15"/>
       <c r="J109" s="15"/>
@@ -36979,13 +36982,13 @@
         <v>370</v>
       </c>
       <c r="Q109" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="R109" s="13" t="s">
         <v>825</v>
       </c>
-      <c r="R109" s="13" t="s">
+      <c r="S109" s="13" t="s">
         <v>826</v>
-      </c>
-      <c r="S109" s="13" t="s">
-        <v>827</v>
       </c>
       <c r="T109" s="24">
         <v>44</v>
@@ -37089,7 +37092,7 @@
         <v>0</v>
       </c>
       <c r="BR109" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS109" s="13" t="s">
         <v>169</v>
@@ -37143,7 +37146,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:100" s="13" customFormat="1" ht="72">
+    <row r="110" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A110" s="12" t="s">
         <v>288</v>
       </c>
@@ -37158,7 +37161,7 @@
         <v>97</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F110" s="14">
         <v>46321</v>
@@ -37168,7 +37171,7 @@
         <v>46334</v>
       </c>
       <c r="H110" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I110" s="15"/>
       <c r="J110" s="15" t="s">
@@ -37178,7 +37181,7 @@
         <v>46364</v>
       </c>
       <c r="L110" s="16" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="M110" s="13">
         <f t="shared" si="31"/>
@@ -37188,16 +37191,16 @@
         <v>46218</v>
       </c>
       <c r="O110" s="27" t="s">
+        <v>1088</v>
+      </c>
+      <c r="P110" s="13" t="s">
         <v>1089</v>
       </c>
-      <c r="P110" s="13" t="s">
+      <c r="Q110" s="17" t="s">
         <v>1090</v>
       </c>
-      <c r="Q110" s="17" t="s">
+      <c r="R110" s="13" t="s">
         <v>1091</v>
-      </c>
-      <c r="R110" s="13" t="s">
-        <v>1092</v>
       </c>
       <c r="T110" s="24">
         <v>20</v>
@@ -37218,7 +37221,7 @@
       </c>
       <c r="Y110" s="28"/>
       <c r="AA110" s="13" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="AC110" s="13" t="s">
         <v>110</v>
@@ -37257,10 +37260,10 @@
         <v>212028</v>
       </c>
       <c r="AO110" s="13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AP110" s="13" t="s">
         <v>1094</v>
-      </c>
-      <c r="AP110" s="13" t="s">
-        <v>1095</v>
       </c>
       <c r="AQ110" s="13" t="s">
         <v>165</v>
@@ -37272,7 +37275,7 @@
         <v>72042190</v>
       </c>
       <c r="AU110" s="13" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AV110" s="16" t="s">
         <v>119</v>
@@ -37281,10 +37284,10 @@
         <v>800</v>
       </c>
       <c r="AX110" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AY110" s="13" t="s">
         <v>1097</v>
-      </c>
-      <c r="AY110" s="13" t="s">
-        <v>1098</v>
       </c>
       <c r="AZ110" s="14">
         <v>46303</v>
@@ -37340,7 +37343,7 @@
       </c>
       <c r="BQ110" s="24"/>
       <c r="BR110" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS110" s="13" t="s">
         <v>169</v>
@@ -37349,13 +37352,13 @@
         <v>124</v>
       </c>
       <c r="BU110" s="13" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="BV110" s="60" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BW110" s="16" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BY110" s="13" t="s">
         <v>380</v>
@@ -37413,7 +37416,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:100" s="13" customFormat="1" ht="100.8">
+    <row r="111" spans="1:100" s="13" customFormat="1" ht="86.4">
       <c r="A111" s="12" t="s">
         <v>288</v>
       </c>
@@ -37428,7 +37431,7 @@
         <v>97</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F111" s="14">
         <v>46277</v>
@@ -37438,7 +37441,7 @@
         <v>46290</v>
       </c>
       <c r="H111" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I111" s="15" t="s">
         <v>100</v>
@@ -37450,7 +37453,7 @@
         <v>46254</v>
       </c>
       <c r="L111" s="16" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="M111" s="13">
         <f t="shared" si="31"/>
@@ -37460,16 +37463,16 @@
         <v>46218</v>
       </c>
       <c r="O111" s="27" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P111" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="P111" s="13" t="s">
+      <c r="Q111" s="17" t="s">
         <v>1103</v>
       </c>
-      <c r="Q111" s="17" t="s">
+      <c r="R111" s="13" t="s">
         <v>1104</v>
-      </c>
-      <c r="R111" s="13" t="s">
-        <v>1105</v>
       </c>
       <c r="T111" s="24">
         <v>75</v>
@@ -37495,19 +37498,19 @@
         <v>110</v>
       </c>
       <c r="AA111" s="13" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="AB111" s="13">
         <v>25.12</v>
       </c>
       <c r="AC111" s="13" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AD111" s="13">
         <v>25.05</v>
       </c>
       <c r="AE111" s="13" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="AF111" s="13">
         <v>25.76</v>
@@ -37531,13 +37534,13 @@
         <v>246</v>
       </c>
       <c r="AN111" s="16" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AO111" s="16" t="s">
         <v>1109</v>
       </c>
-      <c r="AO111" s="16" t="s">
+      <c r="AP111" s="13" t="s">
         <v>1110</v>
-      </c>
-      <c r="AP111" s="13" t="s">
-        <v>1111</v>
       </c>
       <c r="AQ111" s="13" t="s">
         <v>165</v>
@@ -37549,7 +37552,7 @@
         <v>72042190</v>
       </c>
       <c r="AU111" s="13" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AV111" s="16" t="s">
         <v>119</v>
@@ -37558,10 +37561,10 @@
         <v>800</v>
       </c>
       <c r="AX111" s="13" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AY111" s="13" t="s">
         <v>1113</v>
-      </c>
-      <c r="AY111" s="13" t="s">
-        <v>1114</v>
       </c>
       <c r="AZ111" s="27">
         <v>46246</v>
@@ -37637,13 +37640,13 @@
         <v>124</v>
       </c>
       <c r="BU111" s="13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="BV111" s="16" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BW111" s="16" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BX111" s="13" t="s">
         <v>124</v>
@@ -37718,13 +37721,13 @@
         <v>110</v>
       </c>
       <c r="CU111" s="13" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="CV111" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="112" spans="1:100" s="13" customFormat="1" ht="409.6">
+    <row r="112" spans="1:100" s="13" customFormat="1" ht="129.6">
       <c r="A112" s="12" t="s">
         <v>288</v>
       </c>
@@ -37739,7 +37742,7 @@
         <v>97</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F112" s="14">
         <v>46243</v>
@@ -37770,19 +37773,19 @@
         <v>110</v>
       </c>
       <c r="O112" s="16" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="P112" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="Q112" s="17" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R112" s="16" t="s">
         <v>1117</v>
       </c>
-      <c r="R112" s="16" t="s">
+      <c r="S112" s="16" t="s">
         <v>1118</v>
-      </c>
-      <c r="S112" s="16" t="s">
-        <v>1119</v>
       </c>
       <c r="T112" s="13">
         <v>16.431000000000001</v>
@@ -37808,7 +37811,7 @@
         <v>110</v>
       </c>
       <c r="AA112" s="13" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="AB112" s="13">
         <v>16.431000000000001</v>
@@ -37850,22 +37853,22 @@
         <v>1132982</v>
       </c>
       <c r="AO112" s="13" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="AP112" s="13" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AQ112" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR112" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS112" s="16" t="s">
         <v>166</v>
       </c>
       <c r="AU112" s="13" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="AV112" s="13" t="s">
         <v>119</v>
@@ -37874,10 +37877,10 @@
         <v>800</v>
       </c>
       <c r="AX112" s="13" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AY112" s="13" t="s">
         <v>1123</v>
-      </c>
-      <c r="AY112" s="13" t="s">
-        <v>1124</v>
       </c>
       <c r="AZ112" s="14">
         <v>46233</v>
@@ -37952,7 +37955,7 @@
         <v>124</v>
       </c>
       <c r="BU112" s="16" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="BV112" s="16" t="s">
         <v>354</v>
@@ -38037,10 +38040,10 @@
         <v>110</v>
       </c>
       <c r="CU112" s="13" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
-    <row r="113" spans="1:99" s="13" customFormat="1" ht="75" customHeight="1">
+    <row r="113" spans="1:100" s="13" customFormat="1" ht="75" customHeight="1">
       <c r="A113" s="12" t="s">
         <v>288</v>
       </c>
@@ -38055,7 +38058,7 @@
         <v>97</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F113" s="14">
         <v>46251</v>
@@ -38086,19 +38089,19 @@
         <v>110</v>
       </c>
       <c r="O113" s="16" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="P113" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="Q113" s="17" t="s">
+        <v>1126</v>
+      </c>
+      <c r="R113" s="16" t="s">
         <v>1127</v>
       </c>
-      <c r="R113" s="16" t="s">
+      <c r="S113" s="16" t="s">
         <v>1128</v>
-      </c>
-      <c r="S113" s="16" t="s">
-        <v>1129</v>
       </c>
       <c r="T113" s="13">
         <v>16.22</v>
@@ -38124,7 +38127,7 @@
         <v>110</v>
       </c>
       <c r="AA113" s="13" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="AB113" s="13">
         <v>16.22</v>
@@ -38166,34 +38169,34 @@
         <v>1133535</v>
       </c>
       <c r="AO113" s="16" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="AP113" s="13" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AQ113" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR113" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS113" s="16">
         <v>75030010</v>
       </c>
       <c r="AU113" s="13" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AV113" s="24">
+        <v>0</v>
+      </c>
+      <c r="AW113" s="24">
+        <v>0</v>
+      </c>
+      <c r="AX113" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY113" s="13" t="s">
         <v>1132</v>
-      </c>
-      <c r="AV113" s="24">
-        <v>0</v>
-      </c>
-      <c r="AW113" s="24">
-        <v>0</v>
-      </c>
-      <c r="AX113" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="AY113" s="13" t="s">
-        <v>1133</v>
       </c>
       <c r="AZ113" s="14">
         <v>46233</v>
@@ -38267,16 +38270,16 @@
         <v>124</v>
       </c>
       <c r="BU113" s="13" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="BV113" s="13" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="BW113" s="16" t="s">
         <v>127</v>
       </c>
       <c r="BX113" s="13" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="BY113" s="13" t="s">
         <v>124</v>
@@ -38351,10 +38354,10 @@
         <v>110</v>
       </c>
       <c r="CU113" s="13" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
-    <row r="114" spans="1:99" s="13" customFormat="1" ht="144">
+    <row r="114" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A114" s="12" t="s">
         <v>288</v>
       </c>
@@ -38379,7 +38382,7 @@
         <v>46293</v>
       </c>
       <c r="H114" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I114" s="15" t="s">
         <v>172</v>
@@ -38407,7 +38410,7 @@
         <v>102</v>
       </c>
       <c r="Q114" s="17" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="R114" s="13" t="s">
         <v>291</v>
@@ -38433,19 +38436,19 @@
         <v>69840</v>
       </c>
       <c r="Y114" s="19" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Z114" s="14">
         <v>46243</v>
       </c>
       <c r="AA114" s="13" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AB114" s="13">
         <v>23.936</v>
       </c>
       <c r="AC114" s="13" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AD114" s="41">
         <v>23.936</v>
@@ -38472,7 +38475,7 @@
         <v>24000</v>
       </c>
       <c r="AL114" s="16" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="AM114" s="13" t="s">
         <v>246</v>
@@ -38481,16 +38484,16 @@
         <v>20912</v>
       </c>
       <c r="AO114" s="13" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="AP114" s="13" t="s">
         <v>115</v>
       </c>
       <c r="AQ114" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR114" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS114" s="13">
         <v>72042190</v>
@@ -38505,7 +38508,7 @@
         <v>800</v>
       </c>
       <c r="AX114" s="13" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AY114" s="13">
         <v>9000103591</v>
@@ -38570,7 +38573,7 @@
       </c>
       <c r="BQ114" s="24"/>
       <c r="BR114" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS114" s="13" t="s">
         <v>169</v>
@@ -38594,7 +38597,7 @@
         <v>30910</v>
       </c>
       <c r="CA114" s="18" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="CB114" s="22" t="s">
         <v>110</v>
@@ -38647,10 +38650,10 @@
         <v>110</v>
       </c>
       <c r="CU114" s="13" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
-    <row r="115" spans="1:99" s="13" customFormat="1" ht="144">
+    <row r="115" spans="1:100" s="13" customFormat="1" ht="86.4">
       <c r="A115" s="12" t="s">
         <v>288</v>
       </c>
@@ -38659,7 +38662,7 @@
         <v>475480</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>571</v>
+        <v>96</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>97</v>
@@ -38675,13 +38678,13 @@
         <v>46293</v>
       </c>
       <c r="H115" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I115" s="15" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="J115" s="15" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="K115" s="14">
         <v>46259</v>
@@ -38703,7 +38706,7 @@
         <v>102</v>
       </c>
       <c r="Q115" s="17" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="R115" s="13" t="s">
         <v>291</v>
@@ -38734,7 +38737,7 @@
         <v>24.006</v>
       </c>
       <c r="AC115" s="13" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AD115" s="13">
         <v>24.006</v>
@@ -38761,7 +38764,7 @@
         <v>24060</v>
       </c>
       <c r="AL115" s="16" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="AM115" s="13" t="s">
         <v>246</v>
@@ -38770,16 +38773,16 @@
         <v>20911</v>
       </c>
       <c r="AO115" s="13" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="AP115" s="13" t="s">
         <v>115</v>
       </c>
       <c r="AQ115" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR115" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS115" s="13">
         <v>72042190</v>
@@ -38788,7 +38791,7 @@
         <v>117</v>
       </c>
       <c r="AU115" s="13" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="AV115" s="16" t="s">
         <v>119</v>
@@ -38797,7 +38800,7 @@
         <v>800</v>
       </c>
       <c r="AX115" s="13" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AY115" s="13">
         <v>9000103593</v>
@@ -38862,7 +38865,7 @@
       </c>
       <c r="BQ115" s="24"/>
       <c r="BR115" s="13" t="s">
-        <v>582</v>
+        <v>122</v>
       </c>
       <c r="BS115" s="13" t="s">
         <v>169</v>
@@ -38886,7 +38889,7 @@
         <v>30910</v>
       </c>
       <c r="CA115" s="18" t="s">
-        <v>1144</v>
+        <v>130</v>
       </c>
       <c r="CB115" s="22" t="s">
         <v>110</v>
@@ -38907,7 +38910,7 @@
         <v>3786602</v>
       </c>
       <c r="CH115" s="13" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="CI115" s="24">
         <v>95.25</v>
@@ -38935,21 +38938,27 @@
         <v>399235</v>
       </c>
       <c r="CP115" s="24">
-        <v>0</v>
+        <v>1148</v>
       </c>
       <c r="CQ115" s="24">
         <f t="shared" si="34"/>
-        <v>399235</v>
+        <v>400383</v>
       </c>
       <c r="CR115" s="24"/>
+      <c r="CS115" s="14">
+        <v>46288</v>
+      </c>
       <c r="CT115" s="13" t="s">
         <v>110</v>
       </c>
       <c r="CU115" s="13" t="s">
-        <v>1148</v>
+        <v>1147</v>
+      </c>
+      <c r="CV115" s="16" t="s">
+        <v>1173</v>
       </c>
     </row>
-    <row r="116" spans="1:99" s="13" customFormat="1" ht="144">
+    <row r="116" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A116" s="12" t="s">
         <v>288</v>
       </c>
@@ -38967,14 +38976,14 @@
         <v>275622081</v>
       </c>
       <c r="F116" s="14">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="G116" s="43">
         <f>F116+13</f>
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I116" s="15" t="s">
         <v>172</v>
@@ -39002,7 +39011,7 @@
         <v>102</v>
       </c>
       <c r="Q116" s="17" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="R116" s="13" t="s">
         <v>291</v>
@@ -39029,14 +39038,17 @@
       </c>
       <c r="Y116" s="28"/>
       <c r="Z116" s="14"/>
+      <c r="AA116" s="13" t="s">
+        <v>1148</v>
+      </c>
       <c r="AB116" s="13">
         <v>24.53</v>
       </c>
       <c r="AC116" s="13" t="s">
-        <v>1149</v>
-      </c>
-      <c r="AD116" s="13">
-        <v>24.53</v>
+        <v>211</v>
+      </c>
+      <c r="AD116" s="13" t="s">
+        <v>211</v>
       </c>
       <c r="AE116" s="13" t="s">
         <v>110</v>
@@ -39060,7 +39072,7 @@
         <v>24590</v>
       </c>
       <c r="AL116" s="16" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="AM116" s="13" t="s">
         <v>246</v>
@@ -39069,16 +39081,16 @@
         <v>20826</v>
       </c>
       <c r="AO116" s="13" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="AP116" s="13" t="s">
         <v>115</v>
       </c>
       <c r="AQ116" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR116" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS116" s="13">
         <v>72042190</v>
@@ -39087,9 +39099,14 @@
         <v>117</v>
       </c>
       <c r="AV116" s="16" t="s">
-        <v>1151</v>
-      </c>
-      <c r="AW116" s="24"/>
+        <v>119</v>
+      </c>
+      <c r="AW116" s="24">
+        <v>800</v>
+      </c>
+      <c r="AX116" s="13" t="s">
+        <v>1174</v>
+      </c>
       <c r="AY116" s="13">
         <v>9000104195</v>
       </c>
@@ -39150,7 +39167,7 @@
       </c>
       <c r="BQ116" s="24"/>
       <c r="BR116" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS116" s="13" t="s">
         <v>169</v>
@@ -39170,8 +39187,12 @@
       <c r="BY116" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="BZ116" s="24"/>
-      <c r="CA116" s="24"/>
+      <c r="BZ116" s="24">
+        <v>30910</v>
+      </c>
+      <c r="CA116" s="18" t="s">
+        <v>1143</v>
+      </c>
       <c r="CB116" s="22" t="s">
         <v>110</v>
       </c>
@@ -39223,7 +39244,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="117" spans="1:99" s="13" customFormat="1" ht="144">
+    <row r="117" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A117" s="12" t="s">
         <v>288</v>
       </c>
@@ -39235,7 +39256,7 @@
       </c>
       <c r="G117" s="14"/>
       <c r="H117" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I117" s="15"/>
       <c r="J117" s="15"/>
@@ -39254,13 +39275,13 @@
         <v>102</v>
       </c>
       <c r="Q117" s="17" t="s">
+        <v>954</v>
+      </c>
+      <c r="R117" s="13" t="s">
         <v>955</v>
       </c>
-      <c r="R117" s="13" t="s">
+      <c r="S117" s="13" t="s">
         <v>956</v>
-      </c>
-      <c r="S117" s="13" t="s">
-        <v>957</v>
       </c>
       <c r="T117" s="24">
         <v>22</v>
@@ -39313,10 +39334,10 @@
       </c>
       <c r="AN117" s="16"/>
       <c r="AQ117" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR117" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS117" s="13">
         <v>72042190</v>
@@ -39375,7 +39396,7 @@
       </c>
       <c r="BQ117" s="24"/>
       <c r="BR117" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS117" s="13" t="s">
         <v>169</v>
@@ -39440,7 +39461,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="118" spans="1:99" s="13" customFormat="1" ht="144">
+    <row r="118" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A118" s="12" t="s">
         <v>288</v>
       </c>
@@ -39452,7 +39473,7 @@
       </c>
       <c r="G118" s="14"/>
       <c r="H118" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I118" s="15"/>
       <c r="J118" s="15"/>
@@ -39471,13 +39492,13 @@
         <v>102</v>
       </c>
       <c r="Q118" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="R118" s="13" t="s">
         <v>825</v>
       </c>
-      <c r="R118" s="13" t="s">
+      <c r="S118" s="13" t="s">
         <v>826</v>
-      </c>
-      <c r="S118" s="13" t="s">
-        <v>827</v>
       </c>
       <c r="T118" s="24">
         <v>22</v>
@@ -39530,10 +39551,10 @@
       </c>
       <c r="AN118" s="16"/>
       <c r="AQ118" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR118" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS118" s="13">
         <v>72042190</v>
@@ -39592,7 +39613,7 @@
       </c>
       <c r="BQ118" s="24"/>
       <c r="BR118" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS118" s="13" t="s">
         <v>169</v>
@@ -39657,7 +39678,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="119" spans="1:99" s="13" customFormat="1" ht="100.8">
+    <row r="119" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A119" s="12" t="s">
         <v>288</v>
       </c>
@@ -39669,7 +39690,7 @@
       </c>
       <c r="G119" s="14"/>
       <c r="H119" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I119" s="15"/>
       <c r="J119" s="15"/>
@@ -39688,13 +39709,13 @@
         <v>370</v>
       </c>
       <c r="Q119" s="17" t="s">
+        <v>1150</v>
+      </c>
+      <c r="R119" s="16" t="s">
+        <v>1151</v>
+      </c>
+      <c r="S119" s="16" t="s">
         <v>1152</v>
-      </c>
-      <c r="R119" s="16" t="s">
-        <v>1153</v>
-      </c>
-      <c r="S119" s="16" t="s">
-        <v>1154</v>
       </c>
       <c r="T119" s="13">
         <v>21</v>
@@ -39747,10 +39768,10 @@
       </c>
       <c r="AN119" s="16"/>
       <c r="AQ119" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR119" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AT119" s="13" t="s">
         <v>117</v>
@@ -39803,7 +39824,7 @@
       </c>
       <c r="BQ119" s="24"/>
       <c r="BR119" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS119" s="13" t="s">
         <v>169</v>
@@ -39868,7 +39889,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="120" spans="1:99" s="13" customFormat="1">
+    <row r="120" spans="1:100" s="13" customFormat="1">
       <c r="A120" s="12" t="s">
         <v>288</v>
       </c>
@@ -39880,7 +39901,7 @@
       </c>
       <c r="G120" s="14"/>
       <c r="H120" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I120" s="15"/>
       <c r="J120" s="15"/>
@@ -39917,7 +39938,7 @@
       <c r="BP120" s="24"/>
       <c r="BQ120" s="24"/>
       <c r="BR120" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS120" s="13" t="s">
         <v>169</v>
@@ -39968,7 +39989,7 @@
       </c>
       <c r="CR120" s="24"/>
     </row>
-    <row r="121" spans="1:99" s="13" customFormat="1" ht="57.6">
+    <row r="121" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A121" s="12" t="s">
         <v>288</v>
       </c>
@@ -39979,7 +40000,7 @@
         <v>97</v>
       </c>
       <c r="E121" s="32" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="F121" s="14">
         <v>46274</v>
@@ -39989,7 +40010,7 @@
         <v>46287</v>
       </c>
       <c r="H121" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I121" s="15" t="s">
         <v>100</v>
@@ -40005,10 +40026,10 @@
         <v>1</v>
       </c>
       <c r="O121" s="16" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="P121" s="61" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="Q121" s="17"/>
       <c r="V121" s="24"/>
@@ -40016,7 +40037,7 @@
       <c r="X121" s="24"/>
       <c r="Y121" s="28"/>
       <c r="AA121" s="13" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="AK121" s="13">
         <v>24201</v>
@@ -40028,22 +40049,22 @@
         <v>1133531</v>
       </c>
       <c r="AO121" s="13" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="AP121" s="13" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="AQ121" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AR121" s="13" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AS121" s="16" t="s">
         <v>166</v>
       </c>
       <c r="AU121" s="13" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="AV121" s="16" t="s">
         <v>119</v>
@@ -40052,10 +40073,10 @@
         <v>800</v>
       </c>
       <c r="AX121" s="13" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="AY121" s="13" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="AZ121" s="14">
         <v>46262</v>
@@ -40098,7 +40119,7 @@
       <c r="BP121" s="24"/>
       <c r="BQ121" s="24"/>
       <c r="BR121" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS121" s="13" t="s">
         <v>169</v>
@@ -40107,13 +40128,13 @@
         <v>124</v>
       </c>
       <c r="BU121" s="13" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="BV121" s="13" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="BW121" s="16" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="BZ121" s="24">
         <v>29240</v>
@@ -40171,10 +40192,10 @@
         <v>46285</v>
       </c>
       <c r="CT121" s="13" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
-    <row r="122" spans="1:99" s="13" customFormat="1" ht="115.2">
+    <row r="122" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A122" s="13" t="s">
         <v>288</v>
       </c>
@@ -40186,7 +40207,7 @@
       </c>
       <c r="G122" s="14"/>
       <c r="H122" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I122" s="15"/>
       <c r="J122" s="15"/>
@@ -40205,10 +40226,10 @@
         <v>370</v>
       </c>
       <c r="Q122" s="17" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="R122" s="13" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="V122" s="24"/>
       <c r="W122" s="24"/>
@@ -40234,7 +40255,7 @@
       <c r="BP122" s="24"/>
       <c r="BQ122" s="24"/>
       <c r="BR122" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS122" s="13" t="s">
         <v>169</v>
@@ -40285,7 +40306,7 @@
       </c>
       <c r="CR122" s="24"/>
     </row>
-    <row r="123" spans="1:99" s="13" customFormat="1" ht="144">
+    <row r="123" spans="1:100" s="13" customFormat="1" ht="43.2">
       <c r="A123" s="13" t="s">
         <v>288</v>
       </c>
@@ -40297,7 +40318,7 @@
       </c>
       <c r="G123" s="14"/>
       <c r="H123" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I123" s="15"/>
       <c r="J123" s="15"/>
@@ -40316,10 +40337,10 @@
         <v>102</v>
       </c>
       <c r="Q123" s="17" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="R123" s="13" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="T123" s="13">
         <v>50</v>
@@ -40354,7 +40375,7 @@
       <c r="BP123" s="24"/>
       <c r="BQ123" s="24"/>
       <c r="BR123" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS123" s="13" t="s">
         <v>169</v>
@@ -40405,7 +40426,7 @@
       </c>
       <c r="CR123" s="24"/>
     </row>
-    <row r="124" spans="1:99" s="13" customFormat="1" ht="86.4">
+    <row r="124" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A124" s="13" t="s">
         <v>288</v>
       </c>
@@ -40417,7 +40438,7 @@
       </c>
       <c r="G124" s="14"/>
       <c r="H124" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I124" s="15"/>
       <c r="J124" s="15"/>
@@ -40436,7 +40457,7 @@
         <v>370</v>
       </c>
       <c r="Q124" s="17" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="T124" s="13">
         <v>40</v>
@@ -40471,7 +40492,7 @@
       <c r="BP124" s="24"/>
       <c r="BQ124" s="24"/>
       <c r="BR124" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="BS124" s="13" t="s">
         <v>169</v>
@@ -40522,7 +40543,7 @@
       </c>
       <c r="CR124" s="24"/>
     </row>
-    <row r="125" spans="1:99" s="13" customFormat="1" ht="57.6">
+    <row r="125" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A125" s="13" t="s">
         <v>288</v>
       </c>
@@ -40534,7 +40555,7 @@
       </c>
       <c r="G125" s="14"/>
       <c r="H125" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I125" s="15"/>
       <c r="J125" s="15"/>
@@ -40609,7 +40630,7 @@
       </c>
       <c r="CR125" s="24"/>
     </row>
-    <row r="126" spans="1:99" s="13" customFormat="1" ht="72">
+    <row r="126" spans="1:100" s="13" customFormat="1" ht="28.8">
       <c r="A126" s="13" t="s">
         <v>288</v>
       </c>
@@ -40621,7 +40642,7 @@
       </c>
       <c r="G126" s="14"/>
       <c r="H126" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I126" s="15"/>
       <c r="J126" s="15"/>
@@ -40640,10 +40661,10 @@
         <v>370</v>
       </c>
       <c r="Q126" s="17" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="R126" s="13" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="V126" s="24"/>
       <c r="W126" s="24"/>
@@ -40704,7 +40725,7 @@
       </c>
       <c r="CR126" s="24"/>
     </row>
-    <row r="127" spans="1:99" s="13" customFormat="1">
+    <row r="127" spans="1:100" s="13" customFormat="1">
       <c r="A127" s="13" t="s">
         <v>288</v>
       </c>
@@ -40716,7 +40737,7 @@
       </c>
       <c r="G127" s="14"/>
       <c r="H127" s="15" t="s">
-        <v>573</v>
+        <v>99</v>
       </c>
       <c r="I127" s="15"/>
       <c r="J127" s="15"/>
@@ -40792,23 +40813,20 @@
   <mergeCells count="1">
     <mergeCell ref="A1:CV2"/>
   </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="15">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS5" xr:uid="{E1E9FF0D-410B-4587-BFC9-B88B6ADAE82A}">
       <formula1>"Released,In-Transit to Bank,At Bank,In-Transit to CHA,At CHA,At Seller,Pending,Soft Copy Received"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H45 H47:H54 H56:H63 H66 H68:H70 H72 H76 H82:H86 H88:H90 H92 H94:H96 H98:H99 H103 H112:H113" xr:uid="{3592BA6C-4637-4892-B3DF-AAD0AFFF3BA5}">
-      <formula1>"CAD,TT"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV121 AV107 AV82:AV86 AV88:AV90 AV92 AV94:AV101 AV103 AV5:AV28 AV30:AV76 AV110:AV112 AV114:AV116" xr:uid="{5CDAADED-4EEA-4CF6-9831-77FC2C7EC9D8}">
       <formula1>"Filled,Pending"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CA5:CA45 CA121 CA82:CA86 CA88:CA90 CA111:CA115 CA47:CA54 CA66 CA68:CA70 CA75:CA76 CA72 CA56:CA63 CA92 CA94:CA96 CA98:CA99 CA103" xr:uid="{A6F5A0E5-0F22-49D2-B71C-219719C45511}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CA5:CA45 CA121 CA82:CA86 CA88:CA90 CA111:CA116 CA47:CA54 CA66 CA68:CA70 CA75:CA76 CA72 CA56:CA63 CA92 CA94:CA96 CA98:CA99 CA103" xr:uid="{A6F5A0E5-0F22-49D2-B71C-219719C45511}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D127" xr:uid="{2D2AB97F-C76D-41DF-907F-F8CEED097798}">
       <formula1>"MSPL,MSI"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I122:J127 H100:H102 I117:I120 I102 H114:H127 H93 H104:H111 H87 H97 H91 H77:H81 H73:H75 H71 H67 H64:H65 H55 J120 H46 I104:I110" xr:uid="{10262EBC-1B33-427B-92F5-1FBD2FC7F498}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I122:J127 J120 I117:I120 I102 I104:I110" xr:uid="{10262EBC-1B33-427B-92F5-1FBD2FC7F498}">
       <formula1>"Surrenderred,CAD"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C127" xr:uid="{16154F91-A0D4-4BEE-AB3D-BD972A0500E1}">
@@ -40835,6 +40853,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR5:AR20" xr:uid="{76588259-5E51-44E2-B63B-28B2864862E2}">
       <formula1>"MUNDRA, ICD KHODIYAR, NHAVASHEVA, NAGPUR"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H47:H54 H56:H63 H66 H68:H70 H72 H76 H82:H86 H88:H90 H92 H94:H96 H98:H99 H103 H112:H113 H115 H5:H45" xr:uid="{BDA2E582-C0F5-479C-B3E6-D3D8AE394085}">
+      <formula1>"CAD,TT,SWB"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H46 H55 H64:H65 H67 H71 H73:H75 H77:H81 H87 H91 H93 H97 H100:H102 H104:H111 H114 H116:H127" xr:uid="{D477D9D9-FC73-47DA-BA2C-FC85DE5F9A64}">
+      <formula1>"SWB,CAD,TT"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/New Import Monitoring.xlsx
+++ b/data/New Import Monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User-2\Dropbox\Marfani Projects\Marfani Steel Reportings\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6732E89-80D0-4B5B-A2E6-2E5B639AFE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FF974D-6612-4261-A1D5-254367F7DDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A600BC22-BC84-4799-95E7-AAC4792B97D7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Compele Data Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Compele Data Sheet'!$A$3:$CV$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Compele Data Sheet'!$A$3:$CV$128</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5606" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5620" uniqueCount="1182">
   <si>
     <t>Marfani Steel Private Limited</t>
   </si>
@@ -3706,6 +3706,27 @@
   </si>
   <si>
     <t>MOSSIMS210926691496</t>
+  </si>
+  <si>
+    <t>STAINLESS STEEL SCRAP 309 GRADE FOR MELT</t>
+  </si>
+  <si>
+    <t>SS 309</t>
+  </si>
+  <si>
+    <t>NI- 12%-15% CR- 22%-24% FE- Balance</t>
+  </si>
+  <si>
+    <t>HASU1135814</t>
+  </si>
+  <si>
+    <t>(10Jumbo Bag@4 Kg=40Kg)</t>
+  </si>
+  <si>
+    <t>JEDDAH</t>
+  </si>
+  <si>
+    <t>Jawaharlal Nehru</t>
   </si>
 </sst>
 </file>
@@ -4383,7 +4404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5597E4D-E64B-42C2-AB73-4C180426F403}">
-  <dimension ref="A1:CV127"/>
+  <dimension ref="A1:CV128"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -25878,7 +25899,7 @@
         <v>1620021365</v>
       </c>
       <c r="M70" s="13">
-        <f t="shared" ref="M70:M127" si="31">IF(AK70&gt;127000,6,IF(AK70&gt;104000, 5, IF(AK70&gt;79000, 4, IF(AK70&gt;55000, 3, IF(AK70&gt;29000, 2, IF(AK70&gt;4900, 1, 0))))))</f>
+        <f t="shared" ref="M70:M128" si="31">IF(AK70&gt;127000,6,IF(AK70&gt;104000, 5, IF(AK70&gt;79000, 4, IF(AK70&gt;55000, 3, IF(AK70&gt;29000, 2, IF(AK70&gt;4900, 1, 0))))))</f>
         <v>1</v>
       </c>
       <c r="N70" s="43">
@@ -40349,7 +40370,7 @@
         <v>735</v>
       </c>
       <c r="V123" s="24">
-        <f t="shared" ref="V123:V124" si="55">+T123*U123</f>
+        <f t="shared" ref="V123:V128" si="55">+T123*U123</f>
         <v>36750</v>
       </c>
       <c r="W123" s="24"/>
@@ -40571,7 +40592,10 @@
         <v>370</v>
       </c>
       <c r="Q125" s="17"/>
-      <c r="V125" s="24"/>
+      <c r="V125" s="24">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
       <c r="W125" s="24"/>
       <c r="X125" s="24"/>
       <c r="Y125" s="28"/>
@@ -40666,7 +40690,10 @@
       <c r="R126" s="13" t="s">
         <v>1171</v>
       </c>
-      <c r="V126" s="24"/>
+      <c r="V126" s="24">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
       <c r="W126" s="24"/>
       <c r="X126" s="24"/>
       <c r="Y126" s="28"/>
@@ -40750,7 +40777,10 @@
       </c>
       <c r="O127" s="16"/>
       <c r="Q127" s="17"/>
-      <c r="V127" s="24"/>
+      <c r="V127" s="24">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
       <c r="W127" s="24"/>
       <c r="X127" s="24"/>
       <c r="Y127" s="28"/>
@@ -40809,7 +40839,102 @@
       </c>
       <c r="CR127" s="24"/>
     </row>
+    <row r="128" spans="1:100" s="13" customFormat="1" ht="43.2">
+      <c r="A128" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E128" s="13">
+        <v>275759725</v>
+      </c>
+      <c r="F128" s="14">
+        <v>46314</v>
+      </c>
+      <c r="G128" s="14">
+        <f>F128+13</f>
+        <v>46327</v>
+      </c>
+      <c r="I128" s="15"/>
+      <c r="J128" s="15"/>
+      <c r="L128" s="13">
+        <v>1620021640</v>
+      </c>
+      <c r="M128" s="13">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="N128" s="14">
+        <v>46268</v>
+      </c>
+      <c r="O128" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="P128" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q128" s="13" t="s">
+        <v>1175</v>
+      </c>
+      <c r="R128" s="13" t="s">
+        <v>1176</v>
+      </c>
+      <c r="S128" s="13" t="s">
+        <v>1177</v>
+      </c>
+      <c r="T128" s="13">
+        <v>23</v>
+      </c>
+      <c r="U128" s="13">
+        <v>2125</v>
+      </c>
+      <c r="V128" s="24">
+        <f t="shared" si="55"/>
+        <v>48875</v>
+      </c>
+      <c r="Y128" s="13">
+        <v>8110047179</v>
+      </c>
+      <c r="Z128" s="14">
+        <v>46271</v>
+      </c>
+      <c r="AA128" s="13" t="s">
+        <v>1178</v>
+      </c>
+      <c r="AB128" s="13">
+        <v>20.63</v>
+      </c>
+      <c r="AK128" s="13">
+        <v>23630</v>
+      </c>
+      <c r="AL128" s="13" t="s">
+        <v>1179</v>
+      </c>
+      <c r="AM128" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="AN128" s="13">
+        <v>26733</v>
+      </c>
+      <c r="AP128" s="13" t="s">
+        <v>1180</v>
+      </c>
+      <c r="AQ128" s="13" t="s">
+        <v>1181</v>
+      </c>
+      <c r="AR128" s="13" t="s">
+        <v>1181</v>
+      </c>
+      <c r="AS128" s="13">
+        <v>72042190</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:CV128" xr:uid="{E5597E4D-E64B-42C2-AB73-4C180426F403}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:CV2"/>
   </mergeCells>
@@ -40823,16 +40948,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CA5:CA45 CA121 CA82:CA86 CA88:CA90 CA111:CA116 CA47:CA54 CA66 CA68:CA70 CA75:CA76 CA72 CA56:CA63 CA92 CA94:CA96 CA98:CA99 CA103" xr:uid="{A6F5A0E5-0F22-49D2-B71C-219719C45511}">
       <formula1>"Paid,Unpaid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D127" xr:uid="{2D2AB97F-C76D-41DF-907F-F8CEED097798}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D128" xr:uid="{2D2AB97F-C76D-41DF-907F-F8CEED097798}">
       <formula1>"MSPL,MSI"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I122:J127 J120 I117:I120 I102 I104:I110" xr:uid="{10262EBC-1B33-427B-92F5-1FBD2FC7F498}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I104:I110 J120 I117:I120 I102 I122:J128" xr:uid="{10262EBC-1B33-427B-92F5-1FBD2FC7F498}">
       <formula1>"Surrenderred,CAD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C127" xr:uid="{16154F91-A0D4-4BEE-AB3D-BD972A0500E1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C128" xr:uid="{16154F91-A0D4-4BEE-AB3D-BD972A0500E1}">
       <formula1>"Active,Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J112:J119 CH104:CH124 CH5:CH99 I112:I113 I121:J121 I111:J111 I114:J116 I103 I98:I101 I5:J97 J98:J110" xr:uid="{A0AC2255-9F46-4C74-A710-EB7A598AB0D3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CH104:CH124 CH5:CH99 J104:J119 I111:I116 I103:J103 I5:I101 J5:J102 I121:J121" xr:uid="{A0AC2255-9F46-4C74-A710-EB7A598AB0D3}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR27:AR44 AQ5:AQ20 AR22:AR25 AR52:AR55 AQ103:AR105 AQ85:AR99 AR46:AR50 AR57:AR60 AQ22:AQ84 AR62:AR84" xr:uid="{98C578F6-C2B0-46BF-BAB8-DD2E60D0AD78}">
